--- a/tame_output/ON/bt/strategyON_20240830.xlsx
+++ b/tame_output/ON/bt/strategyON_20240830.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>43.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-49.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.7%</t>
+          <t>422.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-689.0%</t>
+          <t>-689.1%</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.5%</t>
+          <t>588.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-299.7%</t>
+          <t>-289.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-170.2%</t>
+          <t>-170.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.922355861194718</v>
+        <v>-2.960468327486224</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.962863803975294</v>
+        <v>1.947618817458691</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.001006550093389</v>
+        <v>0.9628940838018829</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.732766502822962</v>
+        <v>3.709899023048058</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.89540463686823</v>
+        <v>-2.933517103159736</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.98365044735063</v>
+        <v>1.968405460834028</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9777744298296021</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.751700864084335</v>
+        <v>3.728833384309431</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.031357644924547</v>
+        <v>-3.069470111216051</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.113372376273063</v>
+        <v>2.098127389756462</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9777744298296021</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.935803996229295</v>
+        <v>3.912936516454391</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.053765762729419</v>
+        <v>-3.091878229020923</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.096525824054108</v>
+        <v>2.081280837537506</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9777744298296021</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.927920691132288</v>
+        <v>3.905053211357384</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.081989998307019</v>
+        <v>-3.120102464598524</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.087290129372705</v>
+        <v>2.072045142856103</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.033863648572416</v>
+        <v>0.9957511822809106</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.94076074215271</v>
+        <v>3.917893262377807</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.091430924195549</v>
+        <v>-3.129543390487054</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.139767476739141</v>
+        <v>2.124522490222538</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156290766115808</v>
+        <v>1.118178299824302</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.070470730400592</v>
+        <v>4.047603250625689</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.14370453153119</v>
+        <v>-3.181816997822695</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.121749128350185</v>
+        <v>2.106504141833583</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.104017158780167</v>
+        <v>1.065904692488661</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.041997660544508</v>
+        <v>4.019130180769605</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.220034509132096</v>
+        <v>-3.258146975423601</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.089328950203598</v>
+        <v>2.074083963686996</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.104017158780167</v>
+        <v>1.065904692488661</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.040109473438283</v>
+        <v>4.01724199366338</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.422288229456449</v>
+        <v>-3.460400695747954</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.003247691676719</v>
+        <v>1.988002705160117</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9017634384558131</v>
+        <v>0.8636509721643073</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.913577470846533</v>
+        <v>3.89070999107163</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.583856654983705</v>
+        <v>-3.621969121275209</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.937054331675969</v>
+        <v>1.921809345159367</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7749805146579337</v>
+        <v>0.7368680483664279</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.835941726777958</v>
+        <v>3.813074247003055</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.692157316853824</v>
+        <v>-3.730269783145329</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.90680747379384</v>
+        <v>1.891562487277238</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7749805146579337</v>
+        <v>0.7368680483664279</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.849015133643877</v>
+        <v>3.826147653868973</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.785304788157191</v>
+        <v>-3.823417254448696</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.861553682055433</v>
+        <v>1.846308695538831</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6521513033754009</v>
+        <v>0.6140388370838952</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.767322803657297</v>
+        <v>3.744455323882394</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.813205575266664</v>
+        <v>-3.851318041558168</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.848917408338646</v>
+        <v>1.833672421822044</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6175543792324661</v>
+        <v>0.5794419129409604</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.745088690298538</v>
+        <v>3.722221210523635</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.935731677969557</v>
+        <v>-3.973844144261062</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.796671411234687</v>
+        <v>1.781426424718085</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4950282765295723</v>
+        <v>0.4569158102380665</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.668337472654001</v>
+        <v>3.645469992879097</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.166246174155146</v>
+        <v>-4.204358640446651</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.771171572350955</v>
+        <v>1.755926585834353</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2645137803439835</v>
+        <v>0.2264013140524778</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.596734734533151</v>
+        <v>3.573867254758248</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.51499125937959</v>
+        <v>-4.553103725671095</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.771985257263025</v>
+        <v>1.756740270746423</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.11765336013358</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.67179768118366</v>
+        <v>3.648930201408756</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.668977677155731</v>
+        <v>-4.707090143447235</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.779370959298208</v>
+        <v>1.764125972781606</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.11765336013358</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.7407779503293</v>
+        <v>3.717910470554396</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.618455773328065</v>
+        <v>-4.65656823961957</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.785630922949396</v>
+        <v>1.770385936432794</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.11765336013358</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.726829152449421</v>
+        <v>3.703961672674517</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.870930927335789</v>
+        <v>-4.909043393627294</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.69651135040172</v>
+        <v>1.681266363885118</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.11765336013358</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.738699641504835</v>
+        <v>3.715832161729931</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.163826683815201</v>
+        <v>-5.201939150106706</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.580563582328899</v>
+        <v>1.565318595812297</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.11765336013358</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.739910176023778</v>
+        <v>3.717042696248875</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.350490811950009</v>
+        <v>-5.388603278241514</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.510019673302297</v>
+        <v>1.494774686785695</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1290268556005258</v>
+        <v>0.09091438930902007</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.727988535756364</v>
+        <v>3.70512105598146</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.496511498863971</v>
+        <v>-5.534623965155476</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.446689251272901</v>
+        <v>1.431444264756299</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1199437638066689</v>
+        <v>0.0818312975151631</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.717616533416239</v>
+        <v>3.694749053641335</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.588225507973556</v>
+        <v>-5.626337974265061</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.572207704328112</v>
+        <v>1.55696271781151</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1199437638066689</v>
+        <v>0.0818312975151631</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.879820590115283</v>
+        <v>3.856953110340379</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.619877167033525</v>
+        <v>-5.65798963332503</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.554393678667938</v>
+        <v>1.539148692151336</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1147753065622287</v>
+        <v>0.0766628402707229</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.871566153732433</v>
+        <v>3.84869867395753</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.701811985302409</v>
+        <v>-5.739924451593914</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.531849168928876</v>
+        <v>1.516604182412274</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1048405609751485</v>
+        <v>0.06672809468364271</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.875834723948676</v>
+        <v>3.852967244173773</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.803788107550816</v>
+        <v>-5.841900573842321</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.499984358485416</v>
+        <v>1.484739371968813</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.002864438726740914</v>
+        <v>-0.03524802756476486</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.823574689055534</v>
+        <v>3.800707209280631</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.693781824073595</v>
+        <v>-5.7318942903651</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.536139759120479</v>
+        <v>1.520894772603878</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.02606901064401612</v>
+        <v>-0.01204345564748965</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.829650319450074</v>
+        <v>3.806782839675171</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.550722248332669</v>
+        <v>-5.588834714624173</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.597613600138824</v>
+        <v>1.582368613622222</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.0340824372339954</v>
+        <v>-0.004030029057510376</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.838708386126036</v>
+        <v>3.815840906351133</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.249275522860831</v>
+        <v>-5.287387989152336</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.725453173210095</v>
+        <v>1.710208186693493</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3355291627058327</v>
+        <v>0.2974166964143269</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.026837304291675</v>
+        <v>4.003969824516771</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.273865767096015</v>
+        <v>-5.31197823338752</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.716588253268732</v>
+        <v>1.70134326675213</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3355291627058327</v>
+        <v>0.2974166964143269</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.027808482044385</v>
+        <v>4.004941002269482</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.222827391089495</v>
+        <v>-5.260939857381</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.737846508051096</v>
+        <v>1.722601521534494</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3355291627058327</v>
+        <v>0.2974166964143269</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.028651386424141</v>
+        <v>4.005783906649238</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.181688096222864</v>
+        <v>-5.219800562514369</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.773340324871894</v>
+        <v>1.758095338355292</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3766684575724635</v>
+        <v>0.3385559912809577</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.072373062218265</v>
+        <v>4.049505582443361</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.085053184204224</v>
+        <v>-5.123165650495729</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.628178285803284</v>
+        <v>1.612933299286682</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4733033695911034</v>
+        <v>0.4351909032995976</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.946538005553383</v>
+        <v>3.92367052577848</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.215633918735066</v>
+        <v>-5.253746385026571</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.579448036064911</v>
+        <v>1.564203049548309</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3427226350602609</v>
+        <v>0.3046101687687551</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.871691608908842</v>
+        <v>3.848824129133938</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833454</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.051137584544104</v>
+        <v>-5.089250050835609</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.629673388817379</v>
+        <v>1.614428402300776</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5072189692512228</v>
+        <v>0.469106502959717</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.954816228499501</v>
+        <v>3.931948748724598</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.078507517228537</v>
+        <v>-5.116619983520041</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.617913126180035</v>
+        <v>1.602668139663434</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5072189692512228</v>
+        <v>0.469106502959717</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.954003938935931</v>
+        <v>3.931136459161028</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.088892712118426</v>
+        <v>-5.127005178409931</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.623627827349152</v>
+        <v>1.60838284083255</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4968337743613335</v>
+        <v>0.4587213080698277</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.957641601127071</v>
+        <v>3.934774121352167</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.107480870840651</v>
+        <v>-5.145593337132156</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.687029569636687</v>
+        <v>1.671784583120085</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4782456156391081</v>
+        <v>0.4401331493476023</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.01732571167016</v>
+        <v>3.994458231895257</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496549</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.107779417536687</v>
+        <v>-5.145891883828192</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.683779161776572</v>
+        <v>1.668534175259969</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4779470689430722</v>
+        <v>0.4398346026515664</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.014015594470837</v>
+        <v>3.991148114695934</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108852</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.006956283846259</v>
+        <v>-5.045068750137764</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.728639310192134</v>
+        <v>1.713394323675532</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.490411284427426</v>
+        <v>0.4522988181359203</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.026025018700841</v>
+        <v>4.003157538925938</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121461</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.816174923093852</v>
+        <v>-4.854287389385357</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.80508110797164</v>
+        <v>1.789836121455038</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6811926451798334</v>
+        <v>0.6430801788883276</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.140623088630829</v>
+        <v>4.117755608855925</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.797658069052032</v>
+        <v>-4.835770535343537</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.792324695325965</v>
+        <v>1.777079708809363</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6941227746050416</v>
+        <v>0.6560103083135358</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.12821801202355</v>
+        <v>4.105350532248647</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.78576168591298</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.742327481150269</v>
+        <v>-4.780439947441774</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.849423867098728</v>
+        <v>1.834178880582126</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7494533625068037</v>
+        <v>0.7113408962152979</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.196383301376666</v>
+        <v>4.173515821601762</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539889</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.730273354237307</v>
+        <v>-4.768385820528811</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.847932085765351</v>
+        <v>1.832687099248749</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7615074894197665</v>
+        <v>0.7233950231282608</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.197302345425881</v>
+        <v>4.174434865650977</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.771428473805527</v>
+        <v>-4.809540940097032</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.833350668122198</v>
+        <v>1.818105681605596</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7203523698515456</v>
+        <v>0.6822399035600398</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.174489903869084</v>
+        <v>4.151622424094181</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382914</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.668547884276935</v>
+        <v>-4.706660350568439</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.887353929811518</v>
+        <v>1.872108943294916</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.8232329593801385</v>
+        <v>0.7851204930886327</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.249069283464123</v>
+        <v>4.226201803689219</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64685760776031</v>
+        <v>3.646857607760312</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.900148277446435</v>
+        <v>-4.93826074373794</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.814916442717312</v>
+        <v>1.79967145620071</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.8232329593801385</v>
+        <v>0.7851204930886327</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.269271953637717</v>
+        <v>4.246404473862813</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781701</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.918220785738047</v>
+        <v>-4.956333252029552</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.807687439400667</v>
+        <v>1.792442452884065</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.8232329593801385</v>
+        <v>0.7851204930886327</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.269271953637717</v>
+        <v>4.246404473862813</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.67006888808283</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.093327618314492</v>
+        <v>-5.131440084605996</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.697896619963556</v>
+        <v>1.682651633446954</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.8232329593801385</v>
+        <v>0.7851204930886327</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.229523867231183</v>
+        <v>4.20665638745628</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943582</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.062041597774036</v>
+        <v>-5.100154064065541</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.717433647176678</v>
+        <v>1.702188660660076</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8545189799205939</v>
+        <v>0.8164065136290881</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.255318098552396</v>
+        <v>4.232450618777493</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677819</v>
+        <v>3.730590658677821</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.909016205660752</v>
+        <v>-4.947128671952257</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.877814803594896</v>
+        <v>1.862569817078294</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.007544372033878</v>
+        <v>0.9694319057423723</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.446304333393272</v>
+        <v>4.423436853618368</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073878</v>
+        <v>3.74129851807388</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.937323519534022</v>
+        <v>-4.975435985825527</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.053958102953881</v>
+        <v>2.038713116437278</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.007544372033878</v>
+        <v>0.9694319057423723</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.633770558301563</v>
+        <v>4.61090307852666</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903163</v>
+        <v>3.699135800903165</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.103916744647544</v>
+        <v>-5.142029210939049</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.956723764262554</v>
+        <v>1.941478777745952</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8409511469203557</v>
+        <v>0.8028386806288499</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.503217574587532</v>
+        <v>4.480350094812629</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568378</v>
+        <v>3.70820270456838</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.930852365265245</v>
+        <v>-4.968964831556749</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.029625918677191</v>
+        <v>2.01438093216059</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8409511469203557</v>
+        <v>0.8028386806288499</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.50689397724925</v>
+        <v>4.484026497474347</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682201</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.901606384809548</v>
+        <v>-4.939718851101053</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.038942365982965</v>
+        <v>2.023697379466364</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8409511469203557</v>
+        <v>0.8028386806288499</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.504512032372745</v>
+        <v>4.481644552597842</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539103</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.008531932687399</v>
+        <v>-5.046644398978904</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.99346538598946</v>
+        <v>1.978220399472858</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7340255990425043</v>
+        <v>0.6959131327509985</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.437649942803669</v>
+        <v>4.414782463028766</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983733</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.153550491194648</v>
+        <v>-5.191662957486153</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.936886764729795</v>
+        <v>1.921641778213193</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5890070405352558</v>
+        <v>0.55089457424375</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.352067609842555</v>
+        <v>4.329200130067651</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969744</v>
+        <v>3.711872614969746</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.271892256979365</v>
+        <v>-5.31000472327087</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.989481297673661</v>
+        <v>1.974236311157059</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5996930790981458</v>
+        <v>0.5615806128066401</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.458410472238042</v>
+        <v>4.435542992463138</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073534</v>
+        <v>3.714899237073536</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.323302679300073</v>
+        <v>-5.361415145591578</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.966702825871316</v>
+        <v>1.951457839354714</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5996930790981458</v>
+        <v>0.5615806128066401</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.456196169363981</v>
+        <v>4.433328689589077</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720062</v>
+        <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.402722130507825</v>
+        <v>-5.44083459679933</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.934838173462505</v>
+        <v>1.919593186945903</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5996930790981458</v>
+        <v>0.5615806128066401</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.45609929743827</v>
+        <v>4.433231817663366</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581129</v>
+        <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.498185128425042</v>
+        <v>-5.536297594716547</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.896646867853661</v>
+        <v>1.88140188133706</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5996930790981458</v>
+        <v>0.5615806128066401</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.456093190996314</v>
+        <v>4.43322571122141</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500731</v>
+        <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.538205126468826</v>
+        <v>-5.576317592760331</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.878735265198759</v>
+        <v>1.863490278682157</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.559673081054362</v>
+        <v>0.5215606147628562</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.430177588732654</v>
+        <v>4.40731010895775</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636267</v>
+        <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.59357428860102</v>
+        <v>-5.631686754892525</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.862321418093608</v>
+        <v>1.847076431577006</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.559673081054362</v>
+        <v>0.5215606147628562</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.435911406480381</v>
+        <v>4.413043926705477</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73684305539601</v>
+        <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.639012068431847</v>
+        <v>-5.677124534723352</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.84368466950421</v>
+        <v>1.828439682987608</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5168280903762024</v>
+        <v>0.4787156240846965</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.409742775416418</v>
+        <v>4.386875295641514</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396419</v>
+        <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.555786611584183</v>
+        <v>-5.593899077875688</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.896849245093595</v>
+        <v>1.881604258576993</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5168280903762024</v>
+        <v>0.4787156240846965</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.429617168266737</v>
+        <v>4.406749688491833</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299172</v>
+        <v>3.794507029299174</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.379496386978875</v>
+        <v>-5.41760885327038</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.951066035460446</v>
+        <v>1.935821048943843</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5168280903762024</v>
+        <v>0.4787156240846965</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.413317868791465</v>
+        <v>4.390450389016561</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590404</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.19628472384578</v>
+        <v>-5.234397190137285</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.026781650177729</v>
+        <v>2.011536663661127</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5168280903762024</v>
+        <v>0.4787156240846965</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.41574881825551</v>
+        <v>4.392881338480606</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146282</v>
+        <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.124563276831929</v>
+        <v>-5.162675743123434</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.021261414831159</v>
+        <v>2.006016428314557</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.588549537390053</v>
+        <v>0.5504370710985471</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.424572872311709</v>
+        <v>4.401705392536806</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676845</v>
+        <v>3.723809890676847</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.253942059471707</v>
+        <v>-5.292054525763212</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.916425647696419</v>
+        <v>1.901180661179817</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5464477646828496</v>
+        <v>0.5083352983913438</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.34622755460856</v>
+        <v>4.323360074833656</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739462</v>
+        <v>3.715627631739464</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.286958355382452</v>
+        <v>-5.325070821673957</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.088417334217477</v>
+        <v>2.073172347700875</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.477010388016098</v>
+        <v>0.4388979217245922</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.489763333493864</v>
+        <v>4.46689585371896</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.814260545460561</v>
+        <v>3.716691189728145</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.274716278924666</v>
+        <v>-5.275424772876574</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.08523539062884</v>
+        <v>2.084951993048077</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.5379600516076917</v>
+        <v>0.5361150975354922</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.518254357477069</v>
+        <v>4.517147385033749</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240830.xlsx
+++ b/tame_output/ON/bt/strategyON_20240830.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.0%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.6%</t>
+          <t>422.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-689.1%</t>
+          <t>-692.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.7%</t>
+          <t>-169.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.1%</t>
+          <t>588.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-170.4%</t>
+          <t>-174.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.83819962926564</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389346</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814661</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237091</v>
+        <v>3.668289004237089</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.619923016423383</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609749</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973153</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830324</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231804</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700474</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077635</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833452</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077623</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147903</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735275</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496547</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.81564321210885</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121459</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906073</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912978</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539887</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811002</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760312</v>
+        <v>3.646857607760309</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781699</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.670068888082828</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.74559333394358</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677821</v>
+        <v>3.730590658677817</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74129851807388</v>
+        <v>3.741298518073877</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903165</v>
+        <v>3.699135800903162</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.70820270456838</v>
+        <v>3.708202704568376</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682201</v>
+        <v>3.740601586682198</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539104</v>
+        <v>3.699424827539101</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983731</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969746</v>
+        <v>3.711872614969742</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073536</v>
+        <v>3.714899237073532</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720064</v>
+        <v>3.70477813472006</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581131</v>
+        <v>3.736825137581127</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500733</v>
+        <v>3.715393145500729</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636268</v>
+        <v>3.736109598636265</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396012</v>
+        <v>3.736843055396008</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396421</v>
+        <v>3.790292685396417</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299174</v>
+        <v>3.79450702929917</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590402</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146284</v>
+        <v>3.776866743146281</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676847</v>
+        <v>3.723809890676844</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739464</v>
+        <v>3.71562763173946</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.716691189728145</v>
+        <v>3.716691189728142</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.275424772876574</v>
+        <v>-5.313543186024348</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.084951993048077</v>
+        <v>2.069704627788968</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.5361150975354922</v>
+        <v>0.4978985799259548</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.517147385033749</v>
+        <v>4.494217474468027</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240830.xlsx
+++ b/tame_output/ON/bt/strategyON_20240830.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.0%</t>
+          <t>125.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.5%</t>
+          <t>423.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-692.9%</t>
+          <t>-680.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-169.3%</t>
+          <t>-164.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.9%</t>
+          <t>590.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-289.7%</t>
+          <t>-299.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-174.2%</t>
+          <t>-170.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.026452896042961</v>
+        <v>-3.9445477473924</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.007031746192846</v>
+        <v>1.039793805653071</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.978797165481905</v>
+        <v>-3.896892016831344</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.032475795445073</v>
+        <v>1.065237854905298</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.87827900698315</v>
+        <v>-3.796373858332589</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.0775754322193</v>
+        <v>1.110337491679525</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.862373677550798</v>
+        <v>-3.780468528900236</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.070692236468113</v>
+        <v>1.103454295928338</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.817535275942399</v>
+        <v>-3.735630127291838</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.092725299722101</v>
+        <v>1.125487359182326</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
@@ -47137,10 +47137,10 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.837033732184408</v>
+        <v>-3.755128583533847</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.089086856856376</v>
+        <v>1.1218489163166</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.792830895098507</v>
+        <v>-3.710925746447946</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.112647594218573</v>
+        <v>1.145409653678798</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83819962926564</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.800390560935554</v>
+        <v>-3.718485412284993</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.108033728353002</v>
+        <v>1.140795787813226</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.642099143396282</v>
+        <v>-3.560193994745721</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.222598060551751</v>
+        <v>1.255360120011975</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.434457139761806</v>
+        <v>-3.352551991111245</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.304095566599794</v>
+        <v>1.336857626060019</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.383425047039278</v>
+        <v>-3.301519898388717</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.319456631927075</v>
+        <v>1.3522186913873</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.318200865912072</v>
+        <v>-3.236295717261511</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.362733708470663</v>
+        <v>1.395495767930887</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.280773845840938</v>
+        <v>-3.198868697190377</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.373665488798397</v>
+        <v>1.406427548258621</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.300885501875646</v>
+        <v>-3.218980353225085</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.366877618715753</v>
+        <v>1.399639678175978</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069176229144795</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.272472238775763</v>
+        <v>-3.190567090125202</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.538800694976918</v>
+        <v>1.571562754437142</v>
       </c>
       <c r="F1991" t="n">
         <v>1.010200666398366</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.19768997775075</v>
+        <v>-3.115784829100189</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.68882650860474</v>
+        <v>1.721588568064965</v>
       </c>
       <c r="F1992" t="n">
         <v>1.084982927423378</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.171605893486942</v>
+        <v>-3.089700744836381</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.690968118324122</v>
+        <v>1.723730177784347</v>
       </c>
       <c r="F1993" t="n">
         <v>1.084982927423378</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.083727980377822</v>
+        <v>-3.001822831727261</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.72431247915155</v>
+        <v>1.757074538611774</v>
       </c>
       <c r="F1994" t="n">
         <v>1.200908569846729</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.074835518984538</v>
+        <v>-2.992930370333977</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.745423869435655</v>
+        <v>1.778185928895879</v>
       </c>
       <c r="F1995" t="n">
         <v>1.200908569846729</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.243311635954416</v>
+        <v>-3.161406487303855</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.669888470052287</v>
+        <v>1.702650529512512</v>
       </c>
       <c r="F1996" t="n">
         <v>1.172960734130149</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.797055443324976</v>
+        <v>-2.715150294674415</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.829660644291925</v>
+        <v>1.86242270375215</v>
       </c>
       <c r="F1997" t="n">
         <v>1.078242064460516</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.774334339641824</v>
+        <v>-2.692429190991263</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.829413108262091</v>
+        <v>1.862175167722315</v>
       </c>
       <c r="F1998" t="n">
         <v>1.078242064460516</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.903536152935866</v>
+        <v>-2.821631004285305</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.936638508795643</v>
+        <v>1.969400568255868</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9490402511664737</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.929410551409892</v>
+        <v>-2.847505402759331</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.963366571899679</v>
+        <v>1.996128631359904</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9939518598782149</v>
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.960468327486224</v>
+        <v>-2.840450712544157</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.947618817458691</v>
+        <v>1.995625863435518</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9628940838018829</v>
+        <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.709899023048058</v>
+        <v>3.732766502822962</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.933517103159736</v>
+        <v>-2.813499488217669</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.968405460834028</v>
+        <v>2.016412506810855</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9777744298296021</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.728833384309431</v>
+        <v>3.751700864084335</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.069470111216051</v>
+        <v>-2.949452496273985</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.098127389756462</v>
+        <v>2.146134435733288</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9777744298296021</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.912936516454391</v>
+        <v>3.935803996229295</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.091878229020923</v>
+        <v>-2.971860614078857</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.081280837537506</v>
+        <v>2.129287883514333</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9777744298296021</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.905053211357384</v>
+        <v>3.927920691132288</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.120102464598524</v>
+        <v>-3.000084849656458</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.072045142856103</v>
+        <v>2.12005218883293</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9957511822809106</v>
+        <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.917893262377807</v>
+        <v>3.94076074215271</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.129543390487054</v>
+        <v>-3.009525775544988</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.124522490222538</v>
+        <v>2.172529536199365</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.118178299824302</v>
+        <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.047603250625689</v>
+        <v>4.070470730400592</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.181816997822695</v>
+        <v>-3.061799382880629</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.106504141833583</v>
+        <v>2.154511187810409</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.065904692488661</v>
+        <v>1.104017158780167</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.019130180769605</v>
+        <v>4.041997660544508</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.258146975423601</v>
+        <v>-3.138129360481535</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.074083963686996</v>
+        <v>2.122091009663822</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.065904692488661</v>
+        <v>1.104017158780167</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.01724199366338</v>
+        <v>4.040109473438283</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.460400695747954</v>
+        <v>-3.340383080805888</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.988002705160117</v>
+        <v>2.036009751136943</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8636509721643073</v>
+        <v>0.9017634384558131</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.89070999107163</v>
+        <v>3.913577470846533</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.621969121275209</v>
+        <v>-3.501951506333143</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.921809345159367</v>
+        <v>1.969816391136193</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7368680483664279</v>
+        <v>0.7749805146579337</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.813074247003055</v>
+        <v>3.835941726777958</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.730269783145329</v>
+        <v>-3.610252168203263</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.891562487277238</v>
+        <v>1.939569533254064</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7368680483664279</v>
+        <v>0.7749805146579337</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.826147653868973</v>
+        <v>3.849015133643877</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.823417254448696</v>
+        <v>-3.70339963950663</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.846308695538831</v>
+        <v>1.894315741515658</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6140388370838952</v>
+        <v>0.6521513033754009</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.744455323882394</v>
+        <v>3.767322803657297</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.851318041558168</v>
+        <v>-3.731300426616103</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.833672421822044</v>
+        <v>1.88167946779887</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5794419129409604</v>
+        <v>0.6175543792324661</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.722221210523635</v>
+        <v>3.745088690298538</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.973844144261062</v>
+        <v>-3.853826529318996</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.781426424718085</v>
+        <v>1.829433470694911</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4569158102380665</v>
+        <v>0.4950282765295723</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.645469992879097</v>
+        <v>3.668337472654001</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.204358640446651</v>
+        <v>-4.084341025504585</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.755926585834353</v>
+        <v>1.80393363181118</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2264013140524778</v>
+        <v>0.2645137803439835</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.573867254758248</v>
+        <v>3.596734734533151</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814661</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.553103725671095</v>
+        <v>-4.433086110729029</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.756740270746423</v>
+        <v>1.804747316723249</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.11765336013358</v>
+        <v>0.1557658264250857</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.648930201408756</v>
+        <v>3.67179768118366</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237089</v>
+        <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.707090143447235</v>
+        <v>-4.587072528505169</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.764125972781606</v>
+        <v>1.812133018758433</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.11765336013358</v>
+        <v>0.1557658264250857</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.717910470554396</v>
+        <v>3.7407779503293</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423383</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.65656823961957</v>
+        <v>-4.536550624677504</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.770385936432794</v>
+        <v>1.81839298240962</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.11765336013358</v>
+        <v>0.1557658264250857</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.703961672674517</v>
+        <v>3.726829152449421</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609749</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.909043393627294</v>
+        <v>-4.789025778685228</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.681266363885118</v>
+        <v>1.729273409861944</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.11765336013358</v>
+        <v>0.1557658264250857</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.715832161729931</v>
+        <v>3.738699641504835</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973153</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.201939150106706</v>
+        <v>-5.08192153516464</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.565318595812297</v>
+        <v>1.613325641789123</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.11765336013358</v>
+        <v>0.1557658264250857</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.717042696248875</v>
+        <v>3.739910176023778</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.388603278241514</v>
+        <v>-5.268585663299448</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.494774686785695</v>
+        <v>1.542781732762522</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.09091438930902007</v>
+        <v>0.1290268556005258</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.70512105598146</v>
+        <v>3.727988535756364</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.534623965155476</v>
+        <v>-5.41460635021341</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.431444264756299</v>
+        <v>1.479451310733126</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.0818312975151631</v>
+        <v>0.1199437638066689</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.694749053641335</v>
+        <v>3.717616533416239</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830324</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.626337974265061</v>
+        <v>-5.506320359322995</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.55696271781151</v>
+        <v>1.604969763788336</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.0818312975151631</v>
+        <v>0.1199437638066689</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.856953110340379</v>
+        <v>3.879820590115283</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.65798963332503</v>
+        <v>-5.537972018382964</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.539148692151336</v>
+        <v>1.587155738128163</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.0766628402707229</v>
+        <v>0.1147753065622287</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.84869867395753</v>
+        <v>3.871566153732433</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.739924451593914</v>
+        <v>-5.619906836651848</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.516604182412274</v>
+        <v>1.5646112283891</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.06672809468364271</v>
+        <v>0.1048405609751485</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.852967244173773</v>
+        <v>3.875834723948676</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.841900573842321</v>
+        <v>-5.721882958900255</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.484739371968813</v>
+        <v>1.53274641794564</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.03524802756476486</v>
+        <v>0.002864438726740914</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.800707209280631</v>
+        <v>3.823574689055534</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231804</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.7318942903651</v>
+        <v>-5.611876675423034</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.520894772603878</v>
+        <v>1.568901818580704</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.01204345564748965</v>
+        <v>0.02606901064401612</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.806782839675171</v>
+        <v>3.829650319450074</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.588834714624173</v>
+        <v>-5.468817099682107</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.582368613622222</v>
+        <v>1.630375659599049</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.004030029057510376</v>
+        <v>0.0340824372339954</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.815840906351133</v>
+        <v>3.838708386126036</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.287387989152336</v>
+        <v>-5.16737037421027</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.710208186693493</v>
+        <v>1.75821523267032</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2974166964143269</v>
+        <v>0.3355291627058327</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.003969824516771</v>
+        <v>4.026837304291675</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.81263594067962</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.31197823338752</v>
+        <v>-5.191960618445454</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.70134326675213</v>
+        <v>1.749350312728957</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2974166964143269</v>
+        <v>0.3355291627058327</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.004941002269482</v>
+        <v>4.027808482044385</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.260939857381</v>
+        <v>-5.140922242438934</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.722601521534494</v>
+        <v>1.77060856751132</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2974166964143269</v>
+        <v>0.3355291627058327</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.005783906649238</v>
+        <v>4.028651386424141</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969538</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.219800562514369</v>
+        <v>-5.099782947572303</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.758095338355292</v>
+        <v>1.806102384332118</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3385559912809577</v>
+        <v>0.3766684575724635</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.049505582443361</v>
+        <v>4.072373062218265</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700474</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.123165650495729</v>
+        <v>-5.003148035553663</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.612933299286682</v>
+        <v>1.660940345263509</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4351909032995976</v>
+        <v>0.4733033695911034</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.92367052577848</v>
+        <v>3.946538005553383</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077635</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.253746385026571</v>
+        <v>-5.133728770084505</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.564203049548309</v>
+        <v>1.612210095525136</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3046101687687551</v>
+        <v>0.3427226350602609</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.848824129133938</v>
+        <v>3.871691608908842</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833452</v>
+        <v>3.775028860833454</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.089250050835609</v>
+        <v>-4.969232435893543</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.614428402300776</v>
+        <v>1.662435448277603</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.469106502959717</v>
+        <v>0.5072189692512228</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.931948748724598</v>
+        <v>3.954816228499501</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077623</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.116619983520041</v>
+        <v>-4.996602368577975</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.602668139663434</v>
+        <v>1.65067518564026</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.469106502959717</v>
+        <v>0.5072189692512228</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.931136459161028</v>
+        <v>3.954003938935931</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147903</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.127005178409931</v>
+        <v>-5.006987563467865</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.60838284083255</v>
+        <v>1.656389886809376</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4587213080698277</v>
+        <v>0.4968337743613335</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.934774121352167</v>
+        <v>3.957641601127071</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735275</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.145593337132156</v>
+        <v>-5.02557572219009</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.671784583120085</v>
+        <v>1.719791629096912</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4401331493476023</v>
+        <v>0.4782456156391081</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.994458231895257</v>
+        <v>4.01732571167016</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496547</v>
+        <v>3.855120535496549</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.145891883828192</v>
+        <v>-5.025874268886126</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.668534175259969</v>
+        <v>1.716541221236796</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4398346026515664</v>
+        <v>0.4779470689430722</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.991148114695934</v>
+        <v>4.014015594470837</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210885</v>
+        <v>3.815643212108852</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.045068750137764</v>
+        <v>-4.925051135195698</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.713394323675532</v>
+        <v>1.761401369652358</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4522988181359203</v>
+        <v>0.490411284427426</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.003157538925938</v>
+        <v>4.026025018700841</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121459</v>
+        <v>3.807356168121461</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.854287389385357</v>
+        <v>-4.734269774443291</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.789836121455038</v>
+        <v>1.837843167431864</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6430801788883276</v>
+        <v>0.6811926451798334</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.117755608855925</v>
+        <v>4.140623088630829</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906073</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.835770535343537</v>
+        <v>-4.715752920401471</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.777079708809363</v>
+        <v>1.825086754786189</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6560103083135358</v>
+        <v>0.6941227746050416</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.105350532248647</v>
+        <v>4.12821801202355</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912978</v>
+        <v>3.78576168591298</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.780439947441774</v>
+        <v>-4.660422332499708</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.834178880582126</v>
+        <v>1.882185926558952</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7113408962152979</v>
+        <v>0.7494533625068037</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.173515821601762</v>
+        <v>4.196383301376666</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539887</v>
+        <v>3.743767956539889</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.768385820528811</v>
+        <v>-4.648368205586745</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.832687099248749</v>
+        <v>1.880694145225575</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7233950231282608</v>
+        <v>0.7615074894197665</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.174434865650977</v>
+        <v>4.197302345425881</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811002</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.809540940097032</v>
+        <v>-4.689523325154966</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.818105681605596</v>
+        <v>1.866112727582423</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6822399035600398</v>
+        <v>0.7203523698515456</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.151622424094181</v>
+        <v>4.174489903869084</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382913</v>
+        <v>3.612322444382914</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.706660350568439</v>
+        <v>-4.586642735626373</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.872108943294916</v>
+        <v>1.920115989271743</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7851204930886327</v>
+        <v>0.8232329593801385</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.226201803689219</v>
+        <v>4.249069283464123</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760309</v>
+        <v>3.64685760776031</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.93826074373794</v>
+        <v>-4.818243128795874</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.79967145620071</v>
+        <v>1.847678502177536</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7851204930886327</v>
+        <v>0.8232329593801385</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.246404473862813</v>
+        <v>4.269271953637717</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781699</v>
+        <v>3.666767386781701</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.956333252029552</v>
+        <v>-4.836315637087486</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.792442452884065</v>
+        <v>1.840449498860892</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7851204930886327</v>
+        <v>0.8232329593801385</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.246404473862813</v>
+        <v>4.269271953637717</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082828</v>
+        <v>3.67006888808283</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.131440084605996</v>
+        <v>-5.01142246966393</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.682651633446954</v>
+        <v>1.73065867942378</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7851204930886327</v>
+        <v>0.8232329593801385</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.20665638745628</v>
+        <v>4.229523867231183</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74559333394358</v>
+        <v>3.745593333943582</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.100154064065541</v>
+        <v>-4.980136449123475</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.702188660660076</v>
+        <v>1.750195706636903</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8164065136290881</v>
+        <v>0.8545189799205939</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.232450618777493</v>
+        <v>4.255318098552396</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677817</v>
+        <v>3.730590658677819</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.947128671952257</v>
+        <v>-4.827111057010191</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.862569817078294</v>
+        <v>1.910576863055121</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9694319057423723</v>
+        <v>1.007544372033878</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.423436853618368</v>
+        <v>4.446304333393272</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073877</v>
+        <v>3.741298518073878</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.975435985825527</v>
+        <v>-4.855418370883461</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.038713116437278</v>
+        <v>2.086720162414105</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9694319057423723</v>
+        <v>1.007544372033878</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.61090307852666</v>
+        <v>4.633770558301563</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903162</v>
+        <v>3.699135800903163</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.142029210939049</v>
+        <v>-5.022011595996983</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.941478777745952</v>
+        <v>1.989485823722778</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8028386806288499</v>
+        <v>0.8409511469203557</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.480350094812629</v>
+        <v>4.503217574587532</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568376</v>
+        <v>3.708202704568378</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.968964831556749</v>
+        <v>-4.848947216614683</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.01438093216059</v>
+        <v>2.062387978137416</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8028386806288499</v>
+        <v>0.8409511469203557</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.484026497474347</v>
+        <v>4.50689397724925</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682198</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.939718851101053</v>
+        <v>-4.819701236158987</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.023697379466364</v>
+        <v>2.07170442544319</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8028386806288499</v>
+        <v>0.8409511469203557</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.481644552597842</v>
+        <v>4.504512032372745</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539101</v>
+        <v>3.699424827539103</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.046644398978904</v>
+        <v>-4.926626784036838</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.978220399472858</v>
+        <v>2.026227445449685</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6959131327509985</v>
+        <v>0.7340255990425043</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.414782463028766</v>
+        <v>4.437649942803669</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983731</v>
+        <v>3.689962785983733</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.191662957486153</v>
+        <v>-5.071645342544087</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.921641778213193</v>
+        <v>1.969648824190019</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.55089457424375</v>
+        <v>0.5890070405352558</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.329200130067651</v>
+        <v>4.352067609842555</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969742</v>
+        <v>3.711872614969744</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.31000472327087</v>
+        <v>-5.189987108328804</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.974236311157059</v>
+        <v>2.022243357133885</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5615806128066401</v>
+        <v>0.5996930790981458</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.435542992463138</v>
+        <v>4.458410472238042</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073532</v>
+        <v>3.714899237073534</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.361415145591578</v>
+        <v>-5.241397530649512</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.951457839354714</v>
+        <v>1.999464885331541</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5615806128066401</v>
+        <v>0.5996930790981458</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.433328689589077</v>
+        <v>4.456196169363981</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70477813472006</v>
+        <v>3.704778134720062</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.44083459679933</v>
+        <v>-5.320816981857264</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.919593186945903</v>
+        <v>1.96760023292273</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5615806128066401</v>
+        <v>0.5996930790981458</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.433231817663366</v>
+        <v>4.45609929743827</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581127</v>
+        <v>3.736825137581129</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.536297594716547</v>
+        <v>-5.416279979774481</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.88140188133706</v>
+        <v>1.929408927313886</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5615806128066401</v>
+        <v>0.5996930790981458</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.43322571122141</v>
+        <v>4.456093190996314</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500729</v>
+        <v>3.715393145500731</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.576317592760331</v>
+        <v>-5.456299977818265</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.863490278682157</v>
+        <v>1.911497324658983</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5215606147628562</v>
+        <v>0.559673081054362</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.40731010895775</v>
+        <v>4.430177588732654</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636265</v>
+        <v>3.736109598636267</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.631686754892525</v>
+        <v>-5.511669139950459</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.847076431577006</v>
+        <v>1.895083477553832</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5215606147628562</v>
+        <v>0.559673081054362</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.413043926705477</v>
+        <v>4.435911406480381</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396008</v>
+        <v>3.73684305539601</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.677124534723352</v>
+        <v>-5.557106919781286</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.828439682987608</v>
+        <v>1.876446728964434</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4787156240846965</v>
+        <v>0.5168280903762024</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.386875295641514</v>
+        <v>4.409742775416418</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396417</v>
+        <v>3.790292685396419</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.593899077875688</v>
+        <v>-5.473881462933622</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.881604258576993</v>
+        <v>1.929611304553819</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4787156240846965</v>
+        <v>0.5168280903762024</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.406749688491833</v>
+        <v>4.429617168266737</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79450702929917</v>
+        <v>3.794507029299172</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.41760885327038</v>
+        <v>-5.297591238328314</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.935821048943843</v>
+        <v>1.98382809492067</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4787156240846965</v>
+        <v>0.5168280903762024</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.390450389016561</v>
+        <v>4.413317868791465</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590402</v>
+        <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.234397190137285</v>
+        <v>-5.114379575195219</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.011536663661127</v>
+        <v>2.059543709637953</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4787156240846965</v>
+        <v>0.5168280903762024</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.392881338480606</v>
+        <v>4.41574881825551</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146281</v>
+        <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.162675743123434</v>
+        <v>-5.042658128181368</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.006016428314557</v>
+        <v>2.054023474291383</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5504370710985471</v>
+        <v>0.588549537390053</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.401705392536806</v>
+        <v>4.424572872311709</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676844</v>
+        <v>3.723809890676845</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.292054525763212</v>
+        <v>-5.172036910821146</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.901180661179817</v>
+        <v>1.949187707156644</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5083352983913438</v>
+        <v>0.5464477646828496</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.323360074833656</v>
+        <v>4.34622755460856</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.71562763173946</v>
+        <v>3.715627631739462</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.325070821673957</v>
+        <v>-5.205053206731891</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.073172347700875</v>
+        <v>2.121179393677701</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.4388979217245922</v>
+        <v>0.477010388016098</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.46689585371896</v>
+        <v>4.489763333493864</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.716691189728142</v>
+        <v>3.830520470240463</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.313543186024348</v>
+        <v>-5.193525571082282</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.069704627788968</v>
+        <v>2.117711673765794</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.4978985799259548</v>
+        <v>0.5360110462174605</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.494217474468027</v>
+        <v>4.517084954242931</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240830.xlsx
+++ b/tame_output/ON/bt/strategyON_20240830.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>43.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>114.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>124.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.9%</t>
+          <t>422.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-680.9%</t>
+          <t>-692.9%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-164.5%</t>
+          <t>-169.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,11 +1247,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.5%</t>
+          <t>588.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-299.7%</t>
+          <t>-289.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-170.4%</t>
+          <t>-174.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>-20.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2071"/>
+  <dimension ref="A1:G2072"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.9445477473924</v>
+        <v>-4.026452896042961</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.039793805653071</v>
+        <v>1.007031746192846</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.896892016831344</v>
+        <v>-3.978797165481905</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.065237854905298</v>
+        <v>1.032475795445073</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.796373858332589</v>
+        <v>-3.87827900698315</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.110337491679525</v>
+        <v>1.0775754322193</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.780468528900236</v>
+        <v>-3.862373677550798</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.103454295928338</v>
+        <v>1.070692236468113</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.735630127291838</v>
+        <v>-3.817535275942399</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.125487359182326</v>
+        <v>1.092725299722101</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
@@ -47137,10 +47137,10 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.755128583533847</v>
+        <v>-3.837033732184408</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.1218489163166</v>
+        <v>1.089086856856376</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.710925746447946</v>
+        <v>-3.792830895098507</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.145409653678798</v>
+        <v>1.112647594218573</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.83819962926564</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.718485412284993</v>
+        <v>-3.800390560935554</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.140795787813226</v>
+        <v>1.108033728353002</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.560193994745721</v>
+        <v>-3.642099143396282</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.255360120011975</v>
+        <v>1.222598060551751</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.352551991111245</v>
+        <v>-3.434457139761806</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.336857626060019</v>
+        <v>1.304095566599794</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.301519898388717</v>
+        <v>-3.383425047039278</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.3522186913873</v>
+        <v>1.319456631927075</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.236295717261511</v>
+        <v>-3.318200865912072</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.395495767930887</v>
+        <v>1.362733708470663</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.198868697190377</v>
+        <v>-3.280773845840938</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.406427548258621</v>
+        <v>1.373665488798397</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.218980353225085</v>
+        <v>-3.300885501875646</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.399639678175978</v>
+        <v>1.366877618715753</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069176229144795</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.190567090125202</v>
+        <v>-3.272472238775763</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.571562754437142</v>
+        <v>1.538800694976918</v>
       </c>
       <c r="F1991" t="n">
         <v>1.010200666398366</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.115784829100189</v>
+        <v>-3.19768997775075</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.721588568064965</v>
+        <v>1.68882650860474</v>
       </c>
       <c r="F1992" t="n">
         <v>1.084982927423378</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.089700744836381</v>
+        <v>-3.171605893486942</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.723730177784347</v>
+        <v>1.690968118324122</v>
       </c>
       <c r="F1993" t="n">
         <v>1.084982927423378</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.001822831727261</v>
+        <v>-3.083727980377822</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.757074538611774</v>
+        <v>1.72431247915155</v>
       </c>
       <c r="F1994" t="n">
         <v>1.200908569846729</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.992930370333977</v>
+        <v>-3.074835518984538</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.778185928895879</v>
+        <v>1.745423869435655</v>
       </c>
       <c r="F1995" t="n">
         <v>1.200908569846729</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.161406487303855</v>
+        <v>-3.243311635954416</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.702650529512512</v>
+        <v>1.669888470052287</v>
       </c>
       <c r="F1996" t="n">
         <v>1.172960734130149</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.715150294674415</v>
+        <v>-2.797055443324976</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.86242270375215</v>
+        <v>1.829660644291925</v>
       </c>
       <c r="F1997" t="n">
         <v>1.078242064460516</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.692429190991263</v>
+        <v>-2.774334339641824</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.862175167722315</v>
+        <v>1.829413108262091</v>
       </c>
       <c r="F1998" t="n">
         <v>1.078242064460516</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.821631004285305</v>
+        <v>-2.903536152935866</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.969400568255868</v>
+        <v>1.936638508795643</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9490402511664737</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.847505402759331</v>
+        <v>-2.929410551409892</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.996128631359904</v>
+        <v>1.963366571899679</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9939518598782149</v>
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.840450712544157</v>
+        <v>-2.960468327486224</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.995625863435518</v>
+        <v>1.947618817458691</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.001006550093389</v>
+        <v>0.9628940838018829</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.732766502822962</v>
+        <v>3.709899023048058</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.813499488217669</v>
+        <v>-2.933517103159736</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.016412506810855</v>
+        <v>1.968405460834028</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9777744298296021</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.751700864084335</v>
+        <v>3.728833384309431</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.949452496273985</v>
+        <v>-3.069470111216051</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.146134435733288</v>
+        <v>2.098127389756462</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9777744298296021</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.935803996229295</v>
+        <v>3.912936516454391</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.971860614078857</v>
+        <v>-3.091878229020923</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.129287883514333</v>
+        <v>2.081280837537506</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9777744298296021</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.927920691132288</v>
+        <v>3.905053211357384</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.000084849656458</v>
+        <v>-3.120102464598524</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.12005218883293</v>
+        <v>2.072045142856103</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.033863648572416</v>
+        <v>0.9957511822809106</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.94076074215271</v>
+        <v>3.917893262377807</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.009525775544988</v>
+        <v>-3.129543390487054</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.172529536199365</v>
+        <v>2.124522490222538</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156290766115808</v>
+        <v>1.118178299824302</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.070470730400592</v>
+        <v>4.047603250625689</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.061799382880629</v>
+        <v>-3.181816997822695</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.154511187810409</v>
+        <v>2.106504141833583</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.104017158780167</v>
+        <v>1.065904692488661</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.041997660544508</v>
+        <v>4.019130180769605</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.138129360481535</v>
+        <v>-3.258146975423601</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.122091009663822</v>
+        <v>2.074083963686996</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.104017158780167</v>
+        <v>1.065904692488661</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.040109473438283</v>
+        <v>4.01724199366338</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.340383080805888</v>
+        <v>-3.460400695747954</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.036009751136943</v>
+        <v>1.988002705160117</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9017634384558131</v>
+        <v>0.8636509721643073</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.913577470846533</v>
+        <v>3.89070999107163</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.501951506333143</v>
+        <v>-3.621969121275209</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.969816391136193</v>
+        <v>1.921809345159367</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7749805146579337</v>
+        <v>0.7368680483664279</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.835941726777958</v>
+        <v>3.813074247003055</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.610252168203263</v>
+        <v>-3.730269783145329</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.939569533254064</v>
+        <v>1.891562487277238</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7749805146579337</v>
+        <v>0.7368680483664279</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.849015133643877</v>
+        <v>3.826147653868973</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.70339963950663</v>
+        <v>-3.823417254448696</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.894315741515658</v>
+        <v>1.846308695538831</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6521513033754009</v>
+        <v>0.6140388370838952</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.767322803657297</v>
+        <v>3.744455323882394</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.731300426616103</v>
+        <v>-3.851318041558168</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.88167946779887</v>
+        <v>1.833672421822044</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6175543792324661</v>
+        <v>0.5794419129409604</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.745088690298538</v>
+        <v>3.722221210523635</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.853826529318996</v>
+        <v>-3.973844144261062</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.829433470694911</v>
+        <v>1.781426424718085</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4950282765295723</v>
+        <v>0.4569158102380665</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.668337472654001</v>
+        <v>3.645469992879097</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.084341025504585</v>
+        <v>-4.204358640446651</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.80393363181118</v>
+        <v>1.755926585834353</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2645137803439835</v>
+        <v>0.2264013140524778</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.596734734533151</v>
+        <v>3.573867254758248</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.433086110729029</v>
+        <v>-4.553103725671095</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.804747316723249</v>
+        <v>1.756740270746423</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.11765336013358</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.67179768118366</v>
+        <v>3.648930201408756</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.587072528505169</v>
+        <v>-4.707090143447235</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.812133018758433</v>
+        <v>1.764125972781606</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.11765336013358</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.7407779503293</v>
+        <v>3.717910470554396</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.536550624677504</v>
+        <v>-4.65656823961957</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.81839298240962</v>
+        <v>1.770385936432794</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.11765336013358</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.726829152449421</v>
+        <v>3.703961672674517</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.789025778685228</v>
+        <v>-4.909043393627294</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.729273409861944</v>
+        <v>1.681266363885118</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.11765336013358</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.738699641504835</v>
+        <v>3.715832161729931</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.08192153516464</v>
+        <v>-5.201939150106706</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.613325641789123</v>
+        <v>1.565318595812297</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.11765336013358</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.739910176023778</v>
+        <v>3.717042696248875</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.268585663299448</v>
+        <v>-5.388603278241514</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.542781732762522</v>
+        <v>1.494774686785695</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1290268556005258</v>
+        <v>0.09091438930902007</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.727988535756364</v>
+        <v>3.70512105598146</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.41460635021341</v>
+        <v>-5.534623965155476</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.479451310733126</v>
+        <v>1.431444264756299</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1199437638066689</v>
+        <v>0.0818312975151631</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.717616533416239</v>
+        <v>3.694749053641335</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.506320359322995</v>
+        <v>-5.626337974265061</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.604969763788336</v>
+        <v>1.55696271781151</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1199437638066689</v>
+        <v>0.0818312975151631</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.879820590115283</v>
+        <v>3.856953110340379</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.537972018382964</v>
+        <v>-5.65798963332503</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.587155738128163</v>
+        <v>1.539148692151336</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1147753065622287</v>
+        <v>0.0766628402707229</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.871566153732433</v>
+        <v>3.84869867395753</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.619906836651848</v>
+        <v>-5.739924451593914</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.5646112283891</v>
+        <v>1.516604182412274</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1048405609751485</v>
+        <v>0.06672809468364271</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.875834723948676</v>
+        <v>3.852967244173773</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.721882958900255</v>
+        <v>-5.841900573842321</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.53274641794564</v>
+        <v>1.484739371968813</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.002864438726740914</v>
+        <v>-0.03524802756476486</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.823574689055534</v>
+        <v>3.800707209280631</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.611876675423034</v>
+        <v>-5.7318942903651</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.568901818580704</v>
+        <v>1.520894772603878</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.02606901064401612</v>
+        <v>-0.01204345564748965</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.829650319450074</v>
+        <v>3.806782839675171</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.468817099682107</v>
+        <v>-5.588834714624173</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.630375659599049</v>
+        <v>1.582368613622222</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.0340824372339954</v>
+        <v>-0.004030029057510376</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.838708386126036</v>
+        <v>3.815840906351133</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.16737037421027</v>
+        <v>-5.287387989152336</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.75821523267032</v>
+        <v>1.710208186693493</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3355291627058327</v>
+        <v>0.2974166964143269</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.026837304291675</v>
+        <v>4.003969824516771</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.191960618445454</v>
+        <v>-5.31197823338752</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.749350312728957</v>
+        <v>1.70134326675213</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3355291627058327</v>
+        <v>0.2974166964143269</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.027808482044385</v>
+        <v>4.004941002269482</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.140922242438934</v>
+        <v>-5.260939857381</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.77060856751132</v>
+        <v>1.722601521534494</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3355291627058327</v>
+        <v>0.2974166964143269</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.028651386424141</v>
+        <v>4.005783906649238</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.099782947572303</v>
+        <v>-5.219800562514369</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.806102384332118</v>
+        <v>1.758095338355292</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3766684575724635</v>
+        <v>0.3385559912809577</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.072373062218265</v>
+        <v>4.049505582443361</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.003148035553663</v>
+        <v>-5.123165650495729</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.660940345263509</v>
+        <v>1.612933299286682</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4733033695911034</v>
+        <v>0.4351909032995976</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.946538005553383</v>
+        <v>3.92367052577848</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.133728770084505</v>
+        <v>-5.253746385026571</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.612210095525136</v>
+        <v>1.564203049548309</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3427226350602609</v>
+        <v>0.3046101687687551</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.871691608908842</v>
+        <v>3.848824129133938</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833454</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.969232435893543</v>
+        <v>-5.089250050835609</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.662435448277603</v>
+        <v>1.614428402300776</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5072189692512228</v>
+        <v>0.469106502959717</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.954816228499501</v>
+        <v>3.931948748724598</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.996602368577975</v>
+        <v>-5.116619983520041</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.65067518564026</v>
+        <v>1.602668139663434</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5072189692512228</v>
+        <v>0.469106502959717</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.954003938935931</v>
+        <v>3.931136459161028</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.006987563467865</v>
+        <v>-5.127005178409931</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.656389886809376</v>
+        <v>1.60838284083255</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4968337743613335</v>
+        <v>0.4587213080698277</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.957641601127071</v>
+        <v>3.934774121352167</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.02557572219009</v>
+        <v>-5.145593337132156</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.719791629096912</v>
+        <v>1.671784583120085</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4782456156391081</v>
+        <v>0.4401331493476023</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.01732571167016</v>
+        <v>3.994458231895257</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496549</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.025874268886126</v>
+        <v>-5.145891883828192</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.716541221236796</v>
+        <v>1.668534175259969</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4779470689430722</v>
+        <v>0.4398346026515664</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.014015594470837</v>
+        <v>3.991148114695934</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108852</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.925051135195698</v>
+        <v>-5.045068750137764</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.761401369652358</v>
+        <v>1.713394323675532</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.490411284427426</v>
+        <v>0.4522988181359203</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.026025018700841</v>
+        <v>4.003157538925938</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121461</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.734269774443291</v>
+        <v>-4.854287389385357</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.837843167431864</v>
+        <v>1.789836121455038</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6811926451798334</v>
+        <v>0.6430801788883276</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.140623088630829</v>
+        <v>4.117755608855925</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.715752920401471</v>
+        <v>-4.835770535343537</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.825086754786189</v>
+        <v>1.777079708809363</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6941227746050416</v>
+        <v>0.6560103083135358</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.12821801202355</v>
+        <v>4.105350532248647</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.78576168591298</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.660422332499708</v>
+        <v>-4.780439947441774</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.882185926558952</v>
+        <v>1.834178880582126</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7494533625068037</v>
+        <v>0.7113408962152979</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.196383301376666</v>
+        <v>4.173515821601762</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539889</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.648368205586745</v>
+        <v>-4.768385820528811</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.880694145225575</v>
+        <v>1.832687099248749</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7615074894197665</v>
+        <v>0.7233950231282608</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.197302345425881</v>
+        <v>4.174434865650977</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.689523325154966</v>
+        <v>-4.809540940097032</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.866112727582423</v>
+        <v>1.818105681605596</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7203523698515456</v>
+        <v>0.6822399035600398</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.174489903869084</v>
+        <v>4.151622424094181</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382914</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.586642735626373</v>
+        <v>-4.706660350568439</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.920115989271743</v>
+        <v>1.872108943294916</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.8232329593801385</v>
+        <v>0.7851204930886327</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.249069283464123</v>
+        <v>4.226201803689219</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64685760776031</v>
+        <v>3.646857607760312</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.818243128795874</v>
+        <v>-4.93826074373794</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.847678502177536</v>
+        <v>1.79967145620071</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.8232329593801385</v>
+        <v>0.7851204930886327</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.269271953637717</v>
+        <v>4.246404473862813</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781701</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.836315637087486</v>
+        <v>-4.956333252029552</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.840449498860892</v>
+        <v>1.792442452884065</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.8232329593801385</v>
+        <v>0.7851204930886327</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.269271953637717</v>
+        <v>4.246404473862813</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.67006888808283</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.01142246966393</v>
+        <v>-5.131440084605996</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.73065867942378</v>
+        <v>1.682651633446954</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.8232329593801385</v>
+        <v>0.7851204930886327</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.229523867231183</v>
+        <v>4.20665638745628</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943582</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.980136449123475</v>
+        <v>-5.100154064065541</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.750195706636903</v>
+        <v>1.702188660660076</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8545189799205939</v>
+        <v>0.8164065136290881</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.255318098552396</v>
+        <v>4.232450618777493</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677819</v>
+        <v>3.730590658677821</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.827111057010191</v>
+        <v>-4.947128671952257</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.910576863055121</v>
+        <v>1.862569817078294</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.007544372033878</v>
+        <v>0.9694319057423723</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.446304333393272</v>
+        <v>4.423436853618368</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073878</v>
+        <v>3.74129851807388</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.855418370883461</v>
+        <v>-4.975435985825527</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.086720162414105</v>
+        <v>2.038713116437278</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.007544372033878</v>
+        <v>0.9694319057423723</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.633770558301563</v>
+        <v>4.61090307852666</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903163</v>
+        <v>3.699135800903165</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.022011595996983</v>
+        <v>-5.142029210939049</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.989485823722778</v>
+        <v>1.941478777745952</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8409511469203557</v>
+        <v>0.8028386806288499</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.503217574587532</v>
+        <v>4.480350094812629</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568378</v>
+        <v>3.70820270456838</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.848947216614683</v>
+        <v>-4.968964831556749</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.062387978137416</v>
+        <v>2.01438093216059</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8409511469203557</v>
+        <v>0.8028386806288499</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.50689397724925</v>
+        <v>4.484026497474347</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682201</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.819701236158987</v>
+        <v>-4.939718851101053</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.07170442544319</v>
+        <v>2.023697379466364</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8409511469203557</v>
+        <v>0.8028386806288499</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.504512032372745</v>
+        <v>4.481644552597842</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539103</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.926626784036838</v>
+        <v>-5.046644398978904</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.026227445449685</v>
+        <v>1.978220399472858</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7340255990425043</v>
+        <v>0.6959131327509985</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.437649942803669</v>
+        <v>4.414782463028766</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983733</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.071645342544087</v>
+        <v>-5.191662957486153</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.969648824190019</v>
+        <v>1.921641778213193</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5890070405352558</v>
+        <v>0.55089457424375</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.352067609842555</v>
+        <v>4.329200130067651</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969744</v>
+        <v>3.711872614969746</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.189987108328804</v>
+        <v>-5.31000472327087</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.022243357133885</v>
+        <v>1.974236311157059</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5996930790981458</v>
+        <v>0.5615806128066401</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.458410472238042</v>
+        <v>4.435542992463138</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073534</v>
+        <v>3.714899237073536</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.241397530649512</v>
+        <v>-5.361415145591578</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.999464885331541</v>
+        <v>1.951457839354714</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5996930790981458</v>
+        <v>0.5615806128066401</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.456196169363981</v>
+        <v>4.433328689589077</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720062</v>
+        <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.320816981857264</v>
+        <v>-5.44083459679933</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.96760023292273</v>
+        <v>1.919593186945903</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5996930790981458</v>
+        <v>0.5615806128066401</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.45609929743827</v>
+        <v>4.433231817663366</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581129</v>
+        <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.416279979774481</v>
+        <v>-5.536297594716547</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.929408927313886</v>
+        <v>1.88140188133706</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5996930790981458</v>
+        <v>0.5615806128066401</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.456093190996314</v>
+        <v>4.43322571122141</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500731</v>
+        <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.456299977818265</v>
+        <v>-5.576317592760331</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.911497324658983</v>
+        <v>1.863490278682157</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.559673081054362</v>
+        <v>0.5215606147628562</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.430177588732654</v>
+        <v>4.40731010895775</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636267</v>
+        <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.511669139950459</v>
+        <v>-5.631686754892525</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.895083477553832</v>
+        <v>1.847076431577006</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.559673081054362</v>
+        <v>0.5215606147628562</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.435911406480381</v>
+        <v>4.413043926705477</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73684305539601</v>
+        <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.557106919781286</v>
+        <v>-5.677124534723352</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.876446728964434</v>
+        <v>1.828439682987608</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5168280903762024</v>
+        <v>0.4787156240846965</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.409742775416418</v>
+        <v>4.386875295641514</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396419</v>
+        <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.473881462933622</v>
+        <v>-5.593899077875688</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.929611304553819</v>
+        <v>1.881604258576993</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5168280903762024</v>
+        <v>0.4787156240846965</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.429617168266737</v>
+        <v>4.406749688491833</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299172</v>
+        <v>3.794507029299174</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.297591238328314</v>
+        <v>-5.41760885327038</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.98382809492067</v>
+        <v>1.935821048943843</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5168280903762024</v>
+        <v>0.4787156240846965</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.413317868791465</v>
+        <v>4.390450389016561</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590404</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.114379575195219</v>
+        <v>-5.234397190137285</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.059543709637953</v>
+        <v>2.011536663661127</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5168280903762024</v>
+        <v>0.4787156240846965</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.41574881825551</v>
+        <v>4.392881338480606</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146282</v>
+        <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.042658128181368</v>
+        <v>-5.162675743123434</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.054023474291383</v>
+        <v>2.006016428314557</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.588549537390053</v>
+        <v>0.5504370710985471</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.424572872311709</v>
+        <v>4.401705392536806</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676845</v>
+        <v>3.723809890676847</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.172036910821146</v>
+        <v>-5.292054525763212</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.949187707156644</v>
+        <v>1.901180661179817</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5464477646828496</v>
+        <v>0.5083352983913438</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.34622755460856</v>
+        <v>4.323360074833656</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739462</v>
+        <v>3.715627631739464</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.205053206731891</v>
+        <v>-5.325070821673957</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.121179393677701</v>
+        <v>2.073172347700875</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.477010388016098</v>
+        <v>0.4388979217245922</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.489763333493864</v>
+        <v>4.46689585371896</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,45 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.830520470240463</v>
+        <v>3.71378272216641</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.193525571082282</v>
+        <v>-5.313543186024348</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.117711673765794</v>
+        <v>2.069704627788968</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.5360110462174605</v>
+        <v>0.4978985799259548</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.517084954242931</v>
+        <v>4.494217474468027</v>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" s="2" t="n">
+        <v>45534</v>
+      </c>
+      <c r="B2072" t="n">
+        <v>3.716696565505616</v>
+      </c>
+      <c r="C2072" t="n">
+        <v>4.261111920092235</v>
+      </c>
+      <c r="D2072" t="n">
+        <v>-5.313543186024348</v>
+      </c>
+      <c r="E2072" t="n">
+        <v>2.069704627788968</v>
+      </c>
+      <c r="F2072" t="n">
+        <v>0.4978985799259548</v>
+      </c>
+      <c r="G2072" t="n">
+        <v>4.254175717078603</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240830.xlsx
+++ b/tame_output/ON/bt/strategyON_20240830.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>114.5%</t>
+          <t>116.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.9%</t>
+          <t>125.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-41.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.5%</t>
+          <t>422.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-692.9%</t>
+          <t>-698.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-169.3%</t>
+          <t>-171.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.9%</t>
+          <t>588.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-289.7%</t>
+          <t>-295.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-174.2%</t>
+          <t>-182.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-19.1%</t>
         </is>
       </c>
     </row>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.026452896042961</v>
+        <v>-3.9445477473924</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.007031746192846</v>
+        <v>1.039793805653071</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.978797165481905</v>
+        <v>-3.896892016831344</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.032475795445073</v>
+        <v>1.065237854905298</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.87827900698315</v>
+        <v>-3.796373858332589</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.0775754322193</v>
+        <v>1.110337491679525</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.862373677550798</v>
+        <v>-3.780468528900236</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.070692236468113</v>
+        <v>1.103454295928338</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.817535275942399</v>
+        <v>-3.735630127291838</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.092725299722101</v>
+        <v>1.125487359182326</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
@@ -47137,10 +47137,10 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.837033732184408</v>
+        <v>-3.755128583533847</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.089086856856376</v>
+        <v>1.1218489163166</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.792830895098507</v>
+        <v>-3.710925746447946</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.112647594218573</v>
+        <v>1.145409653678798</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83819962926564</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.800390560935554</v>
+        <v>-3.718485412284993</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.108033728353002</v>
+        <v>1.140795787813226</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.642099143396282</v>
+        <v>-3.560193994745721</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.222598060551751</v>
+        <v>1.255360120011975</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.434457139761806</v>
+        <v>-3.352551991111245</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.304095566599794</v>
+        <v>1.336857626060019</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.383425047039278</v>
+        <v>-3.301519898388717</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.319456631927075</v>
+        <v>1.3522186913873</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.318200865912072</v>
+        <v>-3.236295717261511</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.362733708470663</v>
+        <v>1.395495767930887</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.280773845840938</v>
+        <v>-3.198868697190377</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.373665488798397</v>
+        <v>1.406427548258621</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.300885501875646</v>
+        <v>-3.218980353225085</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.366877618715753</v>
+        <v>1.399639678175978</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069176229144795</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.272472238775763</v>
+        <v>-3.190567090125202</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.538800694976918</v>
+        <v>1.571562754437142</v>
       </c>
       <c r="F1991" t="n">
         <v>1.010200666398366</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.19768997775075</v>
+        <v>-3.115784829100189</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.68882650860474</v>
+        <v>1.721588568064965</v>
       </c>
       <c r="F1992" t="n">
         <v>1.084982927423378</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.171605893486942</v>
+        <v>-3.089700744836381</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.690968118324122</v>
+        <v>1.723730177784347</v>
       </c>
       <c r="F1993" t="n">
         <v>1.084982927423378</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.083727980377822</v>
+        <v>-3.001822831727261</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.72431247915155</v>
+        <v>1.757074538611774</v>
       </c>
       <c r="F1994" t="n">
         <v>1.200908569846729</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.074835518984538</v>
+        <v>-2.992930370333977</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.745423869435655</v>
+        <v>1.778185928895879</v>
       </c>
       <c r="F1995" t="n">
         <v>1.200908569846729</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.243311635954416</v>
+        <v>-3.161406487303855</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.669888470052287</v>
+        <v>1.702650529512512</v>
       </c>
       <c r="F1996" t="n">
         <v>1.172960734130149</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.797055443324976</v>
+        <v>-2.715150294674415</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.829660644291925</v>
+        <v>1.86242270375215</v>
       </c>
       <c r="F1997" t="n">
         <v>1.078242064460516</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.774334339641824</v>
+        <v>-2.692429190991263</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.829413108262091</v>
+        <v>1.862175167722315</v>
       </c>
       <c r="F1998" t="n">
         <v>1.078242064460516</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.903536152935866</v>
+        <v>-2.821631004285305</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.936638508795643</v>
+        <v>1.969400568255868</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9490402511664737</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.929410551409892</v>
+        <v>-2.847505402759331</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.963366571899679</v>
+        <v>1.996128631359904</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9939518598782149</v>
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.960468327486224</v>
+        <v>-2.840450712544157</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.947618817458691</v>
+        <v>1.995625863435518</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9628940838018829</v>
+        <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.709899023048058</v>
+        <v>3.732766502822962</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.933517103159736</v>
+        <v>-2.813499488217669</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.968405460834028</v>
+        <v>2.016412506810855</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9777744298296021</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.728833384309431</v>
+        <v>3.751700864084335</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.069470111216051</v>
+        <v>-2.949452496273985</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.098127389756462</v>
+        <v>2.146134435733288</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9777744298296021</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.912936516454391</v>
+        <v>3.935803996229295</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.091878229020923</v>
+        <v>-2.971860614078857</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.081280837537506</v>
+        <v>2.129287883514333</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9777744298296021</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.905053211357384</v>
+        <v>3.927920691132288</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.120102464598524</v>
+        <v>-3.000084849656458</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.072045142856103</v>
+        <v>2.12005218883293</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9957511822809106</v>
+        <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.917893262377807</v>
+        <v>3.94076074215271</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.129543390487054</v>
+        <v>-3.009525775544988</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.124522490222538</v>
+        <v>2.172529536199365</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.118178299824302</v>
+        <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.047603250625689</v>
+        <v>4.070470730400592</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.181816997822695</v>
+        <v>-3.089936908373037</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.106504141833583</v>
+        <v>2.143256177613446</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.065904692488661</v>
+        <v>1.075879633287758</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.019130180769605</v>
+        <v>4.025115145249064</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.258146975423601</v>
+        <v>-3.166266885973943</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.074083963686996</v>
+        <v>2.110835999466859</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.065904692488661</v>
+        <v>1.075879633287758</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.01724199366338</v>
+        <v>4.023226958142839</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.460400695747954</v>
+        <v>-3.368520606298296</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.988002705160117</v>
+        <v>2.02475474093998</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8636509721643073</v>
+        <v>0.873625912963405</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.89070999107163</v>
+        <v>3.896694955551089</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.621969121275209</v>
+        <v>-3.530089031825551</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.921809345159367</v>
+        <v>1.95856138093923</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7368680483664279</v>
+        <v>0.7468429891655256</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.813074247003055</v>
+        <v>3.819059211482513</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389346</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.730269783145329</v>
+        <v>-3.638389693695671</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.891562487277238</v>
+        <v>1.928314523057101</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7368680483664279</v>
+        <v>0.7468429891655256</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.826147653868973</v>
+        <v>3.832132618348432</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.823417254448696</v>
+        <v>-3.731537164999037</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.846308695538831</v>
+        <v>1.883060731318694</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6140388370838952</v>
+        <v>0.6240137778829928</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.744455323882394</v>
+        <v>3.750440288361852</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.851318041558168</v>
+        <v>-3.75943795210851</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.833672421822044</v>
+        <v>1.870424457601907</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5794419129409604</v>
+        <v>0.589416853740058</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.722221210523635</v>
+        <v>3.728206175003093</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.973844144261062</v>
+        <v>-3.881964054811404</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.781426424718085</v>
+        <v>1.818178460497948</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4569158102380665</v>
+        <v>0.4668907510371642</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.645469992879097</v>
+        <v>3.651454957358556</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.204358640446651</v>
+        <v>-4.112478550996993</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.755926585834353</v>
+        <v>1.792678621614217</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2264013140524778</v>
+        <v>0.2363762548515754</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.573867254758248</v>
+        <v>3.579852219237706</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.553103725671095</v>
+        <v>-4.461223636221437</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.756740270746423</v>
+        <v>1.793492306526286</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.11765336013358</v>
+        <v>0.1276283009326776</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.648930201408756</v>
+        <v>3.654915165888215</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237091</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.707090143447235</v>
+        <v>-4.615210053997577</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.764125972781606</v>
+        <v>1.80087800856147</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.11765336013358</v>
+        <v>0.1276283009326776</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.717910470554396</v>
+        <v>3.723895435033855</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.65656823961957</v>
+        <v>-4.564688150169911</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.770385936432794</v>
+        <v>1.807137972212657</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.11765336013358</v>
+        <v>0.1276283009326776</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.703961672674517</v>
+        <v>3.709946637153976</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.909043393627294</v>
+        <v>-4.817163304177636</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.681266363885118</v>
+        <v>1.718018399664981</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.11765336013358</v>
+        <v>0.1276283009326776</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.715832161729931</v>
+        <v>3.72181712620939</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.201939150106706</v>
+        <v>-5.110059060657048</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.565318595812297</v>
+        <v>1.60207063159216</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.11765336013358</v>
+        <v>0.1276283009326776</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.717042696248875</v>
+        <v>3.723027660728333</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.388603278241514</v>
+        <v>-5.296723188791856</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.494774686785695</v>
+        <v>1.531526722565558</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.09091438930902007</v>
+        <v>0.1008893301081177</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.70512105598146</v>
+        <v>3.711106020460919</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.534623965155476</v>
+        <v>-5.442743875705818</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.431444264756299</v>
+        <v>1.468196300536163</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.0818312975151631</v>
+        <v>0.09180623831426077</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.694749053641335</v>
+        <v>3.700734018120794</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.626337974265061</v>
+        <v>-5.534457884815403</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.55696271781151</v>
+        <v>1.593714753591373</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.0818312975151631</v>
+        <v>0.09180623831426077</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.856953110340379</v>
+        <v>3.862938074819838</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.65798963332503</v>
+        <v>-5.566109543875372</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.539148692151336</v>
+        <v>1.575900727931199</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.0766628402707229</v>
+        <v>0.08663778106982056</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.84869867395753</v>
+        <v>3.854683638436988</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.739924451593914</v>
+        <v>-5.648044362144256</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.516604182412274</v>
+        <v>1.553356218192137</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.06672809468364271</v>
+        <v>0.07670303548274038</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.852967244173773</v>
+        <v>3.858952208653231</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.841900573842321</v>
+        <v>-5.750020484392663</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.484739371968813</v>
+        <v>1.521491407748677</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.03524802756476486</v>
+        <v>-0.0252730867656672</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.800707209280631</v>
+        <v>3.806692173760089</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.7318942903651</v>
+        <v>-5.640014200915441</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.520894772603878</v>
+        <v>1.55764680838374</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.01204345564748965</v>
+        <v>-0.002068514848391989</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.806782839675171</v>
+        <v>3.81276780415463</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.588834714624173</v>
+        <v>-5.496954625174515</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.582368613622222</v>
+        <v>1.619120649402086</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.004030029057510376</v>
+        <v>0.005944911741587289</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.815840906351133</v>
+        <v>3.821825870830591</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.287387989152336</v>
+        <v>-5.195507899702678</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.710208186693493</v>
+        <v>1.746960222473356</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2974166964143269</v>
+        <v>0.3073916372134246</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.003969824516771</v>
+        <v>4.00995478899623</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.31197823338752</v>
+        <v>-5.220098143937862</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.70134326675213</v>
+        <v>1.738095302531994</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2974166964143269</v>
+        <v>0.3073916372134246</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.004941002269482</v>
+        <v>4.010925966748941</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.260939857381</v>
+        <v>-5.169059767931341</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.722601521534494</v>
+        <v>1.759353557314357</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2974166964143269</v>
+        <v>0.3073916372134246</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.005783906649238</v>
+        <v>4.011768871128696</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.219800562514369</v>
+        <v>-5.127920473064711</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.758095338355292</v>
+        <v>1.794847374135155</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3385559912809577</v>
+        <v>0.3485309320800554</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.049505582443361</v>
+        <v>4.05549054692282</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.123165650495729</v>
+        <v>-5.03128556104607</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.612933299286682</v>
+        <v>1.649685335066545</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4351909032995976</v>
+        <v>0.4451658440986953</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.92367052577848</v>
+        <v>3.929655490257939</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.253746385026571</v>
+        <v>-5.161866295576913</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.564203049548309</v>
+        <v>1.600955085328172</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3046101687687551</v>
+        <v>0.3145851095678528</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.848824129133938</v>
+        <v>3.854809093613397</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.089250050835609</v>
+        <v>-5.054253067807575</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.614428402300776</v>
+        <v>1.62842719551199</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.469106502959717</v>
+        <v>0.4221983373371907</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.931948748724598</v>
+        <v>3.903803849351082</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.116619983520041</v>
+        <v>-5.081623000492007</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.602668139663434</v>
+        <v>1.616666932874647</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.469106502959717</v>
+        <v>0.4221983373371907</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.931136459161028</v>
+        <v>3.902991559787512</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147906</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.127005178409931</v>
+        <v>-5.092008195381896</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.60838284083255</v>
+        <v>1.622381634043764</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4587213080698277</v>
+        <v>0.4118131424473014</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.934774121352167</v>
+        <v>3.906629221978651</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.145593337132156</v>
+        <v>-5.110596354104121</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.671784583120085</v>
+        <v>1.685783376331299</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4401331493476023</v>
+        <v>0.393224983725076</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.994458231895257</v>
+        <v>3.966313332521741</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.85512053549655</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.145891883828192</v>
+        <v>-5.110894900800157</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.668534175259969</v>
+        <v>1.682532968471183</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4398346026515664</v>
+        <v>0.3929264370290401</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.991148114695934</v>
+        <v>3.963003215322418</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.045068750137764</v>
+        <v>-5.010071767109729</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.713394323675532</v>
+        <v>1.727393116886746</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4522988181359203</v>
+        <v>0.405390652513394</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.003157538925938</v>
+        <v>3.975012639552421</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.854287389385357</v>
+        <v>-4.819290406357322</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.789836121455038</v>
+        <v>1.803834914666252</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6430801788883276</v>
+        <v>0.5961720132658013</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.117755608855925</v>
+        <v>4.089610709482409</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.835770535343537</v>
+        <v>-4.800773552315501</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.777079708809363</v>
+        <v>1.791078502020577</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6560103083135358</v>
+        <v>0.6091021426910095</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.105350532248647</v>
+        <v>4.07720563287513</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.780439947441774</v>
+        <v>-4.745442964413739</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.834178880582126</v>
+        <v>1.84817767379334</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7113408962152979</v>
+        <v>0.6644327305927716</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.173515821601762</v>
+        <v>4.145370922228246</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.768385820528811</v>
+        <v>-4.733388837500776</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.832687099248749</v>
+        <v>1.846685892459963</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7233950231282608</v>
+        <v>0.6764868575057345</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.174434865650977</v>
+        <v>4.146289966277462</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.809540940097032</v>
+        <v>-4.774543957068997</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.818105681605596</v>
+        <v>1.832104474816811</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6822399035600398</v>
+        <v>0.6353317379375135</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.151622424094181</v>
+        <v>4.123477524720665</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.706660350568439</v>
+        <v>-4.671663367540404</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.872108943294916</v>
+        <v>1.88610773650613</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7851204930886327</v>
+        <v>0.7382123274661064</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.226201803689219</v>
+        <v>4.198056904315703</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760312</v>
+        <v>3.646857607760311</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.93826074373794</v>
+        <v>-4.903263760709905</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.79967145620071</v>
+        <v>1.813670249411924</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7851204930886327</v>
+        <v>0.7382123274661064</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.246404473862813</v>
+        <v>4.218259574489298</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781702</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.956333252029552</v>
+        <v>-4.921336269001516</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.792442452884065</v>
+        <v>1.80644124609528</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7851204930886327</v>
+        <v>0.7382123274661064</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.246404473862813</v>
+        <v>4.218259574489298</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.670068888082831</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.131440084605996</v>
+        <v>-5.096443101577961</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.682651633446954</v>
+        <v>1.696650426658168</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7851204930886327</v>
+        <v>0.7382123274661064</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.20665638745628</v>
+        <v>4.178511488082764</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.100154064065541</v>
+        <v>-5.065157081037506</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.702188660660076</v>
+        <v>1.71618745387129</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8164065136290881</v>
+        <v>0.7694983480065618</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.232450618777493</v>
+        <v>4.204305719403977</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677821</v>
+        <v>3.73059065867782</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.947128671952257</v>
+        <v>-4.912131688924221</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.862569817078294</v>
+        <v>1.876568610289509</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9694319057423723</v>
+        <v>0.9225237401198459</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.423436853618368</v>
+        <v>4.395291954244852</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74129851807388</v>
+        <v>3.741298518073879</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.975435985825527</v>
+        <v>-4.940439002797492</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.038713116437278</v>
+        <v>2.052711909648493</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9694319057423723</v>
+        <v>0.9225237401198459</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.61090307852666</v>
+        <v>4.582758179153144</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903165</v>
+        <v>3.699135800903164</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.142029210939049</v>
+        <v>-5.107032227911014</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.941478777745952</v>
+        <v>1.955477570957166</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8028386806288499</v>
+        <v>0.7559305150063236</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.480350094812629</v>
+        <v>4.452205195439113</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.70820270456838</v>
+        <v>3.708202704568379</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.968964831556749</v>
+        <v>-4.933967848528714</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.01438093216059</v>
+        <v>2.028379725371804</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8028386806288499</v>
+        <v>0.7559305150063236</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.484026497474347</v>
+        <v>4.455881598100831</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682201</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.939718851101053</v>
+        <v>-4.904721868073017</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.023697379466364</v>
+        <v>2.037696172677578</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8028386806288499</v>
+        <v>0.7559305150063236</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.481644552597842</v>
+        <v>4.453499653224326</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.046644398978904</v>
+        <v>-5.011647415950868</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.978220399472858</v>
+        <v>1.992219192684072</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6959131327509985</v>
+        <v>0.6490049671284722</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.414782463028766</v>
+        <v>4.386637563655251</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983734</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.191662957486153</v>
+        <v>-5.156665974458117</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.921641778213193</v>
+        <v>1.935640571424407</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.55089457424375</v>
+        <v>0.5039864086212237</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.329200130067651</v>
+        <v>4.301055230694136</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969746</v>
+        <v>3.711872614969745</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.31000472327087</v>
+        <v>-5.275007740242835</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.974236311157059</v>
+        <v>1.988235104368273</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5615806128066401</v>
+        <v>0.5146724471841138</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.435542992463138</v>
+        <v>4.407398093089623</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073536</v>
+        <v>3.714899237073535</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.361415145591578</v>
+        <v>-5.326418162563543</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.951457839354714</v>
+        <v>1.965456632565929</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5615806128066401</v>
+        <v>0.5146724471841138</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.433328689589077</v>
+        <v>4.405183790215562</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720064</v>
+        <v>3.704778134720063</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.44083459679933</v>
+        <v>-5.405837613771294</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.919593186945903</v>
+        <v>1.933591980157118</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5615806128066401</v>
+        <v>0.5146724471841138</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.433231817663366</v>
+        <v>4.405086918289851</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581131</v>
+        <v>3.73682513758113</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.536297594716547</v>
+        <v>-5.501300611688512</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.88140188133706</v>
+        <v>1.895400674548274</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5615806128066401</v>
+        <v>0.5146724471841138</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.43322571122141</v>
+        <v>4.405080811847895</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500733</v>
+        <v>3.715393145500732</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.576317592760331</v>
+        <v>-5.541320609732296</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.863490278682157</v>
+        <v>1.877489071893371</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5215606147628562</v>
+        <v>0.4746524491403299</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.40731010895775</v>
+        <v>4.379165209584235</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.631686754892525</v>
+        <v>-5.596689771864489</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.847076431577006</v>
+        <v>1.86107522478822</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5215606147628562</v>
+        <v>0.4746524491403299</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.413043926705477</v>
+        <v>4.384899027331961</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396012</v>
+        <v>3.736843055396011</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.677124534723352</v>
+        <v>-5.642127551695316</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.828439682987608</v>
+        <v>1.842438476198822</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4787156240846965</v>
+        <v>0.4318074584621703</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.386875295641514</v>
+        <v>4.358730396267998</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396421</v>
+        <v>3.79029268539642</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.593899077875688</v>
+        <v>-5.558902094847652</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.881604258576993</v>
+        <v>1.895603051788207</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4787156240846965</v>
+        <v>0.4318074584621703</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.406749688491833</v>
+        <v>4.378604789118318</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.41760885327038</v>
+        <v>-5.382611870242345</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.935821048943843</v>
+        <v>1.949819842155058</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4787156240846965</v>
+        <v>0.4318074584621703</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.390450389016561</v>
+        <v>4.362305489643045</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.234397190137285</v>
+        <v>-5.19940020710925</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.011536663661127</v>
+        <v>2.025535456872341</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4787156240846965</v>
+        <v>0.4318074584621703</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.392881338480606</v>
+        <v>4.364736439107091</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.162675743123434</v>
+        <v>-5.127678760095399</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.006016428314557</v>
+        <v>2.020015221525771</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5504370710985471</v>
+        <v>0.5035289054760209</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.401705392536806</v>
+        <v>4.373560493163291</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.292054525763212</v>
+        <v>-5.257057542735176</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.901180661179817</v>
+        <v>1.915179454391032</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5083352983913438</v>
+        <v>0.4614271327688176</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.323360074833656</v>
+        <v>4.29521517546014</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.325070821673957</v>
+        <v>-5.290073838645921</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.073172347700875</v>
+        <v>2.087171140912089</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.4388979217245922</v>
+        <v>0.391989756102066</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.46689585371896</v>
+        <v>4.438750954345445</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71378272216641</v>
+        <v>3.713782722166409</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.313543186024348</v>
+        <v>-5.365284771776882</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.069704627788968</v>
+        <v>2.049007993487954</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.4978985799259548</v>
+        <v>0.4166406306314127</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.494217474468027</v>
+        <v>4.445462704891302</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.716696565505616</v>
+        <v>3.743697175344346</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.261111920092235</v>
+        <v>4.276140882633432</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.313543186024348</v>
+        <v>-5.365284771776882</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.069704627788968</v>
+        <v>2.049007993487954</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.4978985799259548</v>
+        <v>0.4166406306314127</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.254175717078603</v>
+        <v>4.2692046796198</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240830.xlsx
+++ b/tame_output/ON/bt/strategyON_20240830.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>125.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.9%</t>
+          <t>423.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-698.1%</t>
+          <t>-692.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-171.3%</t>
+          <t>-169.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.7%</t>
+          <t>589.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-295.1%</t>
+          <t>-292.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-182.3%</t>
+          <t>-173.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -47022,10 +47022,10 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.9445477473924</v>
+        <v>-4.026452896042961</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.039793805653071</v>
+        <v>1.007031746192846</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
@@ -47045,10 +47045,10 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.896892016831344</v>
+        <v>-3.978797165481905</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.065237854905298</v>
+        <v>1.032475795445073</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
@@ -47068,10 +47068,10 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.796373858332589</v>
+        <v>-3.87827900698315</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.110337491679525</v>
+        <v>1.0775754322193</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
@@ -47091,10 +47091,10 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.780468528900236</v>
+        <v>-3.862373677550798</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.103454295928338</v>
+        <v>1.070692236468113</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
@@ -47114,10 +47114,10 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.735630127291838</v>
+        <v>-3.817535275942399</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.125487359182326</v>
+        <v>1.092725299722101</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
@@ -47137,10 +47137,10 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.755128583533847</v>
+        <v>-3.837033732184408</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.1218489163166</v>
+        <v>1.089086856856376</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
@@ -47160,10 +47160,10 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.710925746447946</v>
+        <v>-3.792830895098507</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.145409653678798</v>
+        <v>1.112647594218573</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
@@ -47183,10 +47183,10 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.718485412284993</v>
+        <v>-3.800390560935554</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.140795787813226</v>
+        <v>1.108033728353002</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
@@ -47206,10 +47206,10 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.560193994745721</v>
+        <v>-3.642099143396282</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.255360120011975</v>
+        <v>1.222598060551751</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
@@ -47229,10 +47229,10 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.352551991111245</v>
+        <v>-3.434457139761806</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.336857626060019</v>
+        <v>1.304095566599794</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
@@ -47252,10 +47252,10 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.301519898388717</v>
+        <v>-3.383425047039278</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.3522186913873</v>
+        <v>1.319456631927075</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
@@ -47275,10 +47275,10 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.236295717261511</v>
+        <v>-3.318200865912072</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.395495767930887</v>
+        <v>1.362733708470663</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
@@ -47298,10 +47298,10 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.198868697190377</v>
+        <v>-3.280773845840938</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.406427548258621</v>
+        <v>1.373665488798397</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
@@ -47321,10 +47321,10 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.218980353225085</v>
+        <v>-3.300885501875646</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.399639678175978</v>
+        <v>1.366877618715753</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069176229144795</v>
@@ -47344,10 +47344,10 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.190567090125202</v>
+        <v>-3.272472238775763</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.571562754437142</v>
+        <v>1.538800694976918</v>
       </c>
       <c r="F1991" t="n">
         <v>1.010200666398366</v>
@@ -47367,10 +47367,10 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.115784829100189</v>
+        <v>-3.19768997775075</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.721588568064965</v>
+        <v>1.68882650860474</v>
       </c>
       <c r="F1992" t="n">
         <v>1.084982927423378</v>
@@ -47390,10 +47390,10 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.089700744836381</v>
+        <v>-3.171605893486942</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.723730177784347</v>
+        <v>1.690968118324122</v>
       </c>
       <c r="F1993" t="n">
         <v>1.084982927423378</v>
@@ -47413,10 +47413,10 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.001822831727261</v>
+        <v>-3.083727980377822</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.757074538611774</v>
+        <v>1.72431247915155</v>
       </c>
       <c r="F1994" t="n">
         <v>1.200908569846729</v>
@@ -47436,10 +47436,10 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.992930370333977</v>
+        <v>-3.074835518984538</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.778185928895879</v>
+        <v>1.745423869435655</v>
       </c>
       <c r="F1995" t="n">
         <v>1.200908569846729</v>
@@ -47459,10 +47459,10 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.161406487303855</v>
+        <v>-3.243311635954416</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.702650529512512</v>
+        <v>1.669888470052287</v>
       </c>
       <c r="F1996" t="n">
         <v>1.172960734130149</v>
@@ -47482,10 +47482,10 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.715150294674415</v>
+        <v>-2.797055443324976</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.86242270375215</v>
+        <v>1.829660644291925</v>
       </c>
       <c r="F1997" t="n">
         <v>1.078242064460516</v>
@@ -47505,10 +47505,10 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.692429190991263</v>
+        <v>-2.774334339641824</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.862175167722315</v>
+        <v>1.829413108262091</v>
       </c>
       <c r="F1998" t="n">
         <v>1.078242064460516</v>
@@ -47528,10 +47528,10 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.821631004285305</v>
+        <v>-2.903536152935866</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.969400568255868</v>
+        <v>1.936638508795643</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9490402511664737</v>
@@ -47551,10 +47551,10 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.847505402759331</v>
+        <v>-2.929410551409892</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.996128631359904</v>
+        <v>1.963366571899679</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9939518598782149</v>
@@ -47574,10 +47574,10 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.840450712544157</v>
+        <v>-2.922355861194718</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.995625863435518</v>
+        <v>1.962863803975294</v>
       </c>
       <c r="F2001" t="n">
         <v>1.001006550093389</v>
@@ -47597,10 +47597,10 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.813499488217669</v>
+        <v>-2.89540463686823</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.016412506810855</v>
+        <v>1.98365044735063</v>
       </c>
       <c r="F2002" t="n">
         <v>1.015886896121108</v>
@@ -47620,10 +47620,10 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.949452496273985</v>
+        <v>-3.031357644924547</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.146134435733288</v>
+        <v>2.113372376273063</v>
       </c>
       <c r="F2003" t="n">
         <v>1.015886896121108</v>
@@ -47643,10 +47643,10 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.971860614078857</v>
+        <v>-3.053765762729419</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.129287883514333</v>
+        <v>2.096525824054108</v>
       </c>
       <c r="F2004" t="n">
         <v>1.015886896121108</v>
@@ -47666,10 +47666,10 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.000084849656458</v>
+        <v>-3.081989998307019</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.12005218883293</v>
+        <v>2.087290129372705</v>
       </c>
       <c r="F2005" t="n">
         <v>1.033863648572416</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.009525775544988</v>
+        <v>-3.091430924195549</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.172529536199365</v>
+        <v>2.139767476739141</v>
       </c>
       <c r="F2006" t="n">
         <v>1.156290766115808</v>
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.089936908373037</v>
+        <v>-3.175885312816829</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.143256177613446</v>
+        <v>2.108876815835929</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.075879633287758</v>
+        <v>1.071836377494528</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.025115145249064</v>
+        <v>4.022689191773125</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.166266885973943</v>
+        <v>-3.252215290417735</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.110835999466859</v>
+        <v>2.076456637689342</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.075879633287758</v>
+        <v>1.071836377494528</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.023226958142839</v>
+        <v>4.0208010046669</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.368520606298296</v>
+        <v>-3.454469010742088</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.02475474093998</v>
+        <v>1.990375379162463</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.873625912963405</v>
+        <v>0.8695826571701744</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.896694955551089</v>
+        <v>3.89426900207515</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.530089031825551</v>
+        <v>-3.616037436269343</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.95856138093923</v>
+        <v>1.924182019161713</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7468429891655256</v>
+        <v>0.742799733372295</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.819059211482513</v>
+        <v>3.816633258006575</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.638389693695671</v>
+        <v>-3.724338098139463</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.928314523057101</v>
+        <v>1.893935161279584</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7468429891655256</v>
+        <v>0.742799733372295</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.832132618348432</v>
+        <v>3.829706664872494</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.731537164999037</v>
+        <v>-3.817485569442829</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.883060731318694</v>
+        <v>1.848681369541177</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6240137778829928</v>
+        <v>0.6199705220897622</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.750440288361852</v>
+        <v>3.748014334885914</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.75943795210851</v>
+        <v>-3.845386356552302</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.870424457601907</v>
+        <v>1.83604509582439</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.589416853740058</v>
+        <v>0.5853735979468274</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.728206175003093</v>
+        <v>3.725780221527155</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.881964054811404</v>
+        <v>-3.967912459255196</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.818178460497948</v>
+        <v>1.783799098720432</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4668907510371642</v>
+        <v>0.4628474952439335</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.651454957358556</v>
+        <v>3.649029003882617</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.112478550996993</v>
+        <v>-4.198426955440785</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.792678621614217</v>
+        <v>1.7582992598367</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2363762548515754</v>
+        <v>0.2323329990583448</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.579852219237706</v>
+        <v>3.577426265761768</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.461223636221437</v>
+        <v>-4.547172040665228</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.793492306526286</v>
+        <v>1.759112944748769</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1276283009326776</v>
+        <v>0.123585045139447</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.654915165888215</v>
+        <v>3.652489212412276</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.615210053997577</v>
+        <v>-4.701158458441369</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.80087800856147</v>
+        <v>1.766498646783953</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1276283009326776</v>
+        <v>0.123585045139447</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.723895435033855</v>
+        <v>3.721469481557916</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.564688150169911</v>
+        <v>-4.650636554613703</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.807137972212657</v>
+        <v>1.77275861043514</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1276283009326776</v>
+        <v>0.123585045139447</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.709946637153976</v>
+        <v>3.707520683678037</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.817163304177636</v>
+        <v>-4.903111708621427</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.718018399664981</v>
+        <v>1.683639037887465</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1276283009326776</v>
+        <v>0.123585045139447</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.72181712620939</v>
+        <v>3.719391172733451</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.110059060657048</v>
+        <v>-5.196007465100839</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.60207063159216</v>
+        <v>1.567691269814643</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1276283009326776</v>
+        <v>0.123585045139447</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.723027660728333</v>
+        <v>3.720601707252395</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.296723188791856</v>
+        <v>-5.382671593235647</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.531526722565558</v>
+        <v>1.497147360788042</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1008893301081177</v>
+        <v>0.09684607431488712</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.711106020460919</v>
+        <v>3.70868006698498</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.442743875705818</v>
+        <v>-5.52869228014961</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.468196300536163</v>
+        <v>1.433816938758646</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.09180623831426077</v>
+        <v>0.08776298252103015</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.700734018120794</v>
+        <v>3.698308064644856</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.534457884815403</v>
+        <v>-5.620406289259195</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.593714753591373</v>
+        <v>1.559335391813856</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.09180623831426077</v>
+        <v>0.08776298252103015</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.862938074819838</v>
+        <v>3.8605121213439</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.566109543875372</v>
+        <v>-5.652057948319165</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.575900727931199</v>
+        <v>1.541521366153682</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.08663778106982056</v>
+        <v>0.08259452527658995</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.854683638436988</v>
+        <v>3.85225768496105</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.648044362144256</v>
+        <v>-5.733992766588048</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.553356218192137</v>
+        <v>1.51897685641462</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.07670303548274038</v>
+        <v>0.07265977968950976</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.858952208653231</v>
+        <v>3.856526255177293</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332687</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.750020484392663</v>
+        <v>-5.835968888836455</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.521491407748677</v>
+        <v>1.48711204597116</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.0252730867656672</v>
+        <v>-0.02931634255889781</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.806692173760089</v>
+        <v>3.804266220284151</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.640014200915441</v>
+        <v>-5.725962605359234</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.55764680838374</v>
+        <v>1.523267446606224</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.002068514848391989</v>
+        <v>-0.006111770641622605</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.81276780415463</v>
+        <v>3.810341850678691</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.496954625174515</v>
+        <v>-5.582903029618308</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.619120649402086</v>
+        <v>1.584741287624568</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.005944911741587289</v>
+        <v>0.001901655948356673</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.821825870830591</v>
+        <v>3.819399917354653</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.195507899702678</v>
+        <v>-5.28145630414647</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.746960222473356</v>
+        <v>1.712580860695839</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3073916372134246</v>
+        <v>0.3033483814201939</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.00995478899623</v>
+        <v>4.007528835520292</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.220098143937862</v>
+        <v>-5.306046548381654</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.738095302531994</v>
+        <v>1.703715940754476</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3073916372134246</v>
+        <v>0.3033483814201939</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.010925966748941</v>
+        <v>4.008500013273002</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.169059767931341</v>
+        <v>-5.255008172375134</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.759353557314357</v>
+        <v>1.72497419553684</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3073916372134246</v>
+        <v>0.3033483814201939</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.011768871128696</v>
+        <v>4.009342917652758</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.127920473064711</v>
+        <v>-5.213868877508503</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.794847374135155</v>
+        <v>1.760468012357638</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3485309320800554</v>
+        <v>0.3444876762868248</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.05549054692282</v>
+        <v>4.053064593446882</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700474</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.03128556104607</v>
+        <v>-5.117233965489863</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.649685335066545</v>
+        <v>1.615305973289029</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4451658440986953</v>
+        <v>0.4411225883054647</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.929655490257939</v>
+        <v>3.927229536782</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.161866295576913</v>
+        <v>-5.247814700020705</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.600955085328172</v>
+        <v>1.566575723550656</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3145851095678528</v>
+        <v>0.3105418537746222</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.854809093613397</v>
+        <v>3.852383140137459</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.054253067807575</v>
+        <v>-5.083318365829744</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.62842719551199</v>
+        <v>1.616801076303123</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4221983373371907</v>
+        <v>0.4750381879655841</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.903803849351082</v>
+        <v>3.935507759728118</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077624</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.081623000492007</v>
+        <v>-5.110688298514176</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.616666932874647</v>
+        <v>1.60504081366578</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4221983373371907</v>
+        <v>0.4750381879655841</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.902991559787512</v>
+        <v>3.934695470164548</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147906</v>
+        <v>3.832307024147904</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.092008195381896</v>
+        <v>-5.121073493404065</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.622381634043764</v>
+        <v>1.610755514834897</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4118131424473014</v>
+        <v>0.4646529930756947</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.906629221978651</v>
+        <v>3.938333132355686</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.110596354104121</v>
+        <v>-5.13966165212629</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.685783376331299</v>
+        <v>1.674157257122431</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.393224983725076</v>
+        <v>0.4460648343534694</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.966313332521741</v>
+        <v>3.998017242898777</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.85512053549655</v>
+        <v>3.855120535496548</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.110894900800157</v>
+        <v>-5.139960198822326</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.682532968471183</v>
+        <v>1.670906849262316</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3929264370290401</v>
+        <v>0.4457662876574335</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.963003215322418</v>
+        <v>3.994707125699454</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108851</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.010071767109729</v>
+        <v>-5.039137065131898</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.727393116886746</v>
+        <v>1.715766997677878</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.405390652513394</v>
+        <v>0.4582305031417873</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.975012639552421</v>
+        <v>4.006716549929457</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.80735616812146</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.819290406357322</v>
+        <v>-4.848355704379491</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.803834914666252</v>
+        <v>1.792208795457384</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5961720132658013</v>
+        <v>0.6490118638941946</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.089610709482409</v>
+        <v>4.121314619859445</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.800773552315501</v>
+        <v>-4.829838850337671</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.791078502020577</v>
+        <v>1.779452382811709</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6091021426910095</v>
+        <v>0.6619419933194028</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.07720563287513</v>
+        <v>4.108909543252167</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.745442964413739</v>
+        <v>-4.774508262435909</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.84817767379334</v>
+        <v>1.836551554584472</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6644327305927716</v>
+        <v>0.717272581221165</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.145370922228246</v>
+        <v>4.177074832605283</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.733388837500776</v>
+        <v>-4.762454135522946</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.846685892459963</v>
+        <v>1.835059773251095</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6764868575057345</v>
+        <v>0.7293267081341278</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.146289966277462</v>
+        <v>4.177993876654498</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.774543957068997</v>
+        <v>-4.803609255091167</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.832104474816811</v>
+        <v>1.820478355607943</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6353317379375135</v>
+        <v>0.6881715885659069</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.123477524720665</v>
+        <v>4.155181435097701</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.671663367540404</v>
+        <v>-4.700728665562574</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.88610773650613</v>
+        <v>1.874481617297262</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7382123274661064</v>
+        <v>0.7910521780944998</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.198056904315703</v>
+        <v>4.22976081469274</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760311</v>
+        <v>3.646857607760309</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.903263760709905</v>
+        <v>-4.932329058732075</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.813670249411924</v>
+        <v>1.802044130203056</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7382123274661064</v>
+        <v>0.7910521780944998</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.218259574489298</v>
+        <v>4.249963484866334</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781702</v>
+        <v>3.6667673867817</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.921336269001516</v>
+        <v>-4.950401567023686</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.80644124609528</v>
+        <v>1.794815126886412</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7382123274661064</v>
+        <v>0.7910521780944998</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.218259574489298</v>
+        <v>4.249963484866334</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082831</v>
+        <v>3.670068888082829</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.096443101577961</v>
+        <v>-5.125508399600131</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.696650426658168</v>
+        <v>1.685024307449301</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7382123274661064</v>
+        <v>0.7910521780944998</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.178511488082764</v>
+        <v>4.2102153984598</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943581</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.065157081037506</v>
+        <v>-5.094222379059675</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.71618745387129</v>
+        <v>1.704561334662423</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7694983480065618</v>
+        <v>0.8223381986349552</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.204305719403977</v>
+        <v>4.236009629781013</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73059065867782</v>
+        <v>3.730590658677818</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.912131688924221</v>
+        <v>-4.941196986946391</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.876568610289509</v>
+        <v>1.864942491080641</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9225237401198459</v>
+        <v>0.9753635907482393</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.395291954244852</v>
+        <v>4.426995864621889</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073879</v>
+        <v>3.741298518073878</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.940439002797492</v>
+        <v>-4.969504300819661</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.052711909648493</v>
+        <v>2.041085790439625</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9225237401198459</v>
+        <v>0.9753635907482393</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.582758179153144</v>
+        <v>4.61446208953018</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903164</v>
+        <v>3.699135800903163</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.107032227911014</v>
+        <v>-5.136097525933184</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.955477570957166</v>
+        <v>1.943851451748298</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7559305150063236</v>
+        <v>0.8087703656347169</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.452205195439113</v>
+        <v>4.483909105816149</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568379</v>
+        <v>3.708202704568377</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.933967848528714</v>
+        <v>-4.963033146550884</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.028379725371804</v>
+        <v>2.016753606162936</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7559305150063236</v>
+        <v>0.8087703656347169</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.455881598100831</v>
+        <v>4.487585508477867</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682199</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.904721868073017</v>
+        <v>-4.933787166095187</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.037696172677578</v>
+        <v>2.02607005346871</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7559305150063236</v>
+        <v>0.8087703656347169</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.453499653224326</v>
+        <v>4.485203563601362</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539104</v>
+        <v>3.699424827539102</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.011647415950868</v>
+        <v>-5.040712713973038</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.992219192684072</v>
+        <v>1.980593073475204</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6490049671284722</v>
+        <v>0.7018448177568656</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.386637563655251</v>
+        <v>4.418341474032286</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983734</v>
+        <v>3.689962785983732</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.156665974458117</v>
+        <v>-5.185731272480287</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.935640571424407</v>
+        <v>1.924014452215539</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5039864086212237</v>
+        <v>0.556826259249617</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.301055230694136</v>
+        <v>4.332759141071172</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969745</v>
+        <v>3.711872614969743</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.275007740242835</v>
+        <v>-5.304073038265004</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.988235104368273</v>
+        <v>1.976608985159405</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5146724471841138</v>
+        <v>0.5675122978125071</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.407398093089623</v>
+        <v>4.439102003466658</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073535</v>
+        <v>3.714899237073533</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.326418162563543</v>
+        <v>-5.355483460585712</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.965456632565929</v>
+        <v>1.95383051335706</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5146724471841138</v>
+        <v>0.5675122978125071</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.405183790215562</v>
+        <v>4.436887700592597</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720063</v>
+        <v>3.704778134720061</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.405837613771294</v>
+        <v>-5.434902911793464</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.933591980157118</v>
+        <v>1.921965860948249</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5146724471841138</v>
+        <v>0.5675122978125071</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.405086918289851</v>
+        <v>4.436790828666886</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.73682513758113</v>
+        <v>3.736825137581128</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.501300611688512</v>
+        <v>-5.530365909710682</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.895400674548274</v>
+        <v>1.883774555339406</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5146724471841138</v>
+        <v>0.5675122978125071</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.405080811847895</v>
+        <v>4.43678472222493</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500732</v>
+        <v>3.71539314550073</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.541320609732296</v>
+        <v>-5.570385907754465</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.877489071893371</v>
+        <v>1.865862952684503</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.4746524491403299</v>
+        <v>0.5274922997687232</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.379165209584235</v>
+        <v>4.410869119961271</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636268</v>
+        <v>3.736109598636266</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.596689771864489</v>
+        <v>-5.625755069886659</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.86107522478822</v>
+        <v>1.849449105579352</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.4746524491403299</v>
+        <v>0.5274922997687232</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.384899027331961</v>
+        <v>4.416602937708998</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396011</v>
+        <v>3.736843055396009</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.642127551695316</v>
+        <v>-5.671192849717486</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.842438476198822</v>
+        <v>1.830812356989954</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4318074584621703</v>
+        <v>0.4846473090905636</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.358730396267998</v>
+        <v>4.390434306645035</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.79029268539642</v>
+        <v>3.790292685396418</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.558902094847652</v>
+        <v>-5.587967392869822</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.895603051788207</v>
+        <v>1.883976932579339</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4318074584621703</v>
+        <v>0.4846473090905636</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.378604789118318</v>
+        <v>4.410308699495354</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299174</v>
+        <v>3.794507029299172</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.382611870242345</v>
+        <v>-5.411677168264514</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.949819842155058</v>
+        <v>1.93819372294619</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4318074584621703</v>
+        <v>0.4846473090905636</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.362305489643045</v>
+        <v>4.394009400020082</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.19940020710925</v>
+        <v>-5.228465505131419</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.025535456872341</v>
+        <v>2.013909337663474</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4318074584621703</v>
+        <v>0.4846473090905636</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.364736439107091</v>
+        <v>4.396440349484127</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146284</v>
+        <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.127678760095399</v>
+        <v>-5.156744058117568</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.020015221525771</v>
+        <v>2.008389102316903</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5035289054760209</v>
+        <v>0.5563687561044142</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.373560493163291</v>
+        <v>4.405264403540326</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676847</v>
+        <v>3.723809890676845</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.257057542735176</v>
+        <v>-5.286122840757346</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.915179454391032</v>
+        <v>1.903553335182164</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.4614271327688176</v>
+        <v>0.5142669833972109</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.29521517546014</v>
+        <v>4.326919085837176</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739464</v>
+        <v>3.715627631739462</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.290073838645921</v>
+        <v>-5.319139136668091</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.087171140912089</v>
+        <v>2.075545021703221</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.391989756102066</v>
+        <v>0.4448296067304593</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.438750954345445</v>
+        <v>4.47045486472248</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166409</v>
+        <v>3.713782722166407</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.365284771776882</v>
+        <v>-5.307611501018482</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.049007993487954</v>
+        <v>2.072077301791314</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.4166406306314127</v>
+        <v>0.5038302649318218</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.445462704891302</v>
+        <v>4.497776485471547</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,19 +49201,19 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.743697175344346</v>
+        <v>3.743697175344344</v>
       </c>
       <c r="C2072" t="n">
         <v>4.276140882633432</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.365284771776882</v>
+        <v>-5.307611501018482</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.049007993487954</v>
+        <v>2.072077301791314</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.4166406306314127</v>
+        <v>0.5038302649318218</v>
       </c>
       <c r="G2072" t="n">
         <v>4.2692046796198</v>

--- a/tame_output/ON/bt/strategyON_20240830.xlsx
+++ b/tame_output/ON/bt/strategyON_20240830.xlsx
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.81263594067962</v>
+        <v>3.812635940679621</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969538</v>
+        <v>3.831734516969539</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700474</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833454</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077624</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147904</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496548</v>
+        <v>3.85512053549655</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108851</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.80735616812146</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912979</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539888</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811003</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382913</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760309</v>
+        <v>3.646857607760311</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.6667673867817</v>
+        <v>3.666767386781702</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082829</v>
+        <v>3.670068888082831</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943581</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677818</v>
+        <v>3.73059065867782</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073878</v>
+        <v>3.741298518073879</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903163</v>
+        <v>3.699135800903164</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568377</v>
+        <v>3.708202704568379</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682199</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539102</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983732</v>
+        <v>3.689962785983734</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969743</v>
+        <v>3.711872614969745</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073533</v>
+        <v>3.714899237073535</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720061</v>
+        <v>3.704778134720063</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581128</v>
+        <v>3.73682513758113</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.71539314550073</v>
+        <v>3.715393145500732</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636266</v>
+        <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396009</v>
+        <v>3.736843055396011</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396418</v>
+        <v>3.79029268539642</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299172</v>
+        <v>3.794507029299174</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590404</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146282</v>
+        <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676845</v>
+        <v>3.723809890676847</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739462</v>
+        <v>3.715627631739464</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166407</v>
+        <v>3.713782722166409</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.743697175344344</v>
+        <v>3.743697175344346</v>
       </c>
       <c r="C2072" t="n">
         <v>4.276140882633432</v>

--- a/tame_output/ON/bt/strategyON_20240830.xlsx
+++ b/tame_output/ON/bt/strategyON_20240830.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>42.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>116.0%</t>
+          <t>116.2%</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.0%</t>
+          <t>125.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.0%</t>
+          <t>422.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-692.3%</t>
+          <t>-691.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-169.0%</t>
+          <t>-160.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.1%</t>
+          <t>588.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-173.6%</t>
+          <t>-173.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
     </row>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332687</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679621</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969539</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833454</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832307024147906</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.85512053549655</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760311</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781702</v>
+        <v>3.666767386781704</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082831</v>
+        <v>3.670068888082833</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943584</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73059065867782</v>
+        <v>3.730590658677822</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073879</v>
+        <v>3.741298518073881</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903164</v>
+        <v>3.699135800903166</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568379</v>
+        <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682202</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539104</v>
+        <v>3.699424827539105</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983734</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969745</v>
+        <v>3.711872614969747</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073535</v>
+        <v>3.714899237073537</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720063</v>
+        <v>3.704778134720065</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.73682513758113</v>
+        <v>3.736825137581132</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500732</v>
+        <v>3.715393145500734</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636268</v>
+        <v>3.736109598636269</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396011</v>
+        <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.79029268539642</v>
+        <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299174</v>
+        <v>3.794507029299176</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590407</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146284</v>
+        <v>3.776866743146286</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676847</v>
+        <v>3.723809890676849</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739464</v>
+        <v>3.715627631739466</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166409</v>
+        <v>3.71378272216641</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.743697175344346</v>
+        <v>3.703539972471331</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.276140882633432</v>
+        <v>4.278021184104387</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.307611501018482</v>
+        <v>-5.298197278927402</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.072077301791314</v>
+        <v>2.158385848219678</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.5038302649318218</v>
+        <v>0.5070942028287871</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.2692046796198</v>
+        <v>4.582277705801659</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240830.xlsx
+++ b/tame_output/ON/bt/strategyON_20240830.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>116.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.5%</t>
+          <t>423.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-691.4%</t>
+          <t>-677.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.4%</t>
+          <t>-154.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.3%</t>
+          <t>590.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-292.2%</t>
+          <t>-308.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-173.3%</t>
+          <t>-164.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.175885312816829</v>
+        <v>-3.14370453153119</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.108876815835929</v>
+        <v>2.121749128350185</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.071836377494528</v>
+        <v>1.104017158780167</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.022689191773125</v>
+        <v>4.041997660544508</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.252215290417735</v>
+        <v>-3.220034509132096</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.076456637689342</v>
+        <v>2.089328950203598</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.071836377494528</v>
+        <v>1.104017158780167</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.0208010046669</v>
+        <v>4.040109473438283</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.454469010742088</v>
+        <v>-3.315431071819159</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.990375379162463</v>
+        <v>2.045990554731635</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8695826571701744</v>
+        <v>1.008620596093104</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.89426900207515</v>
+        <v>3.977691765428908</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.616037436269343</v>
+        <v>-3.476999497346414</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.924182019161713</v>
+        <v>1.979797194730885</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.742799733372295</v>
+        <v>0.8818376722952247</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.816633258006575</v>
+        <v>3.900056021360333</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389346</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.724338098139463</v>
+        <v>-3.585300159216533</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.893935161279584</v>
+        <v>1.949550336848756</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.742799733372295</v>
+        <v>0.8818376722952247</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.829706664872494</v>
+        <v>3.913129428226251</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.817485569442829</v>
+        <v>-3.6784476305199</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.848681369541177</v>
+        <v>1.904296545110349</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6199705220897622</v>
+        <v>0.7590084610126919</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.748014334885914</v>
+        <v>3.831437098239672</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.845386356552302</v>
+        <v>-3.706348417629373</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.83604509582439</v>
+        <v>1.891660271393562</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5853735979468274</v>
+        <v>0.7244115368697571</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.725780221527155</v>
+        <v>3.809202984880913</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.967912459255196</v>
+        <v>-3.828874520332267</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.783799098720432</v>
+        <v>1.839414274289603</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4628474952439335</v>
+        <v>0.6018854341668632</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.649029003882617</v>
+        <v>3.732451767236376</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.198426955440785</v>
+        <v>-4.059389016517856</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.7582992598367</v>
+        <v>1.813914435405871</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2323329990583448</v>
+        <v>0.3713709379812745</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.577426265761768</v>
+        <v>3.660849029115526</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.547172040665228</v>
+        <v>-4.408134101742299</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.759112944748769</v>
+        <v>1.814728120317941</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.123585045139447</v>
+        <v>0.2626229840623767</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.652489212412276</v>
+        <v>3.735911975766034</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237091</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.701158458441369</v>
+        <v>-4.56212051951844</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.766498646783953</v>
+        <v>1.822113822353125</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.123585045139447</v>
+        <v>0.2626229840623767</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.721469481557916</v>
+        <v>3.804892244911674</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.650636554613703</v>
+        <v>-4.511598615690774</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.77275861043514</v>
+        <v>1.828373786004312</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.123585045139447</v>
+        <v>0.2626229840623767</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.707520683678037</v>
+        <v>3.790943447031795</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.903111708621427</v>
+        <v>-4.764073769698498</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.683639037887465</v>
+        <v>1.739254213456636</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.123585045139447</v>
+        <v>0.2626229840623767</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.719391172733451</v>
+        <v>3.802813936087209</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.196007465100839</v>
+        <v>-5.056969526177911</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.567691269814643</v>
+        <v>1.623306445383815</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.123585045139447</v>
+        <v>0.2626229840623767</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.720601707252395</v>
+        <v>3.804024470606153</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.382671593235647</v>
+        <v>-5.243633654312719</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.497147360788042</v>
+        <v>1.552762536357213</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.09684607431488712</v>
+        <v>0.2358840132378168</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.70868006698498</v>
+        <v>3.792102830338738</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.52869228014961</v>
+        <v>-5.389654341226681</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.433816938758646</v>
+        <v>1.489432114327818</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.08776298252103015</v>
+        <v>0.2268009214439599</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.698308064644856</v>
+        <v>3.781730827998613</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.620406289259195</v>
+        <v>-5.481368350336266</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.559335391813856</v>
+        <v>1.614950567383028</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.08776298252103015</v>
+        <v>0.2268009214439599</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.8605121213439</v>
+        <v>3.943934884697658</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.652057948319165</v>
+        <v>-5.513020009396236</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.541521366153682</v>
+        <v>1.597136541722854</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.08259452527658995</v>
+        <v>0.2216324641995197</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.85225768496105</v>
+        <v>3.935680448314808</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.733992766588048</v>
+        <v>-5.594954827665119</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.51897685641462</v>
+        <v>1.574592031983792</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.07265977968950976</v>
+        <v>0.2116977186124395</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.856526255177293</v>
+        <v>3.939949018531051</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.835968888836455</v>
+        <v>-5.696930949913527</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.48711204597116</v>
+        <v>1.542727221540331</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.02931634255889781</v>
+        <v>0.1097215963640319</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.804266220284151</v>
+        <v>3.887688983637909</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.725962605359234</v>
+        <v>-5.586924666436305</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.523267446606224</v>
+        <v>1.578882622175395</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.006111770641622605</v>
+        <v>0.1329261682813071</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.810341850678691</v>
+        <v>3.893764614032449</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.582903029618308</v>
+        <v>-5.443865090695379</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.584741287624568</v>
+        <v>1.64035646319374</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.001901655948356673</v>
+        <v>0.1409395948712864</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.819399917354653</v>
+        <v>3.902822680708411</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.28145630414647</v>
+        <v>-5.142418365223541</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.712580860695839</v>
+        <v>1.768196036265011</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3033483814201939</v>
+        <v>0.4423863203431236</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.007528835520292</v>
+        <v>4.090951598874049</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.306046548381654</v>
+        <v>-5.167008609458725</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.703715940754476</v>
+        <v>1.759331116323648</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3033483814201939</v>
+        <v>0.4423863203431236</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.008500013273002</v>
+        <v>4.09192277662676</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.255008172375134</v>
+        <v>-5.115970233452205</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.72497419553684</v>
+        <v>1.780589371106012</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3033483814201939</v>
+        <v>0.4423863203431236</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.009342917652758</v>
+        <v>4.092765681006515</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.213868877508503</v>
+        <v>-5.074830938585574</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.760468012357638</v>
+        <v>1.81608318792681</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3444876762868248</v>
+        <v>0.4835256152097545</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.053064593446882</v>
+        <v>4.13648735680064</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.117233965489863</v>
+        <v>-4.978196026566934</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.615305973289029</v>
+        <v>1.6709211488582</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4411225883054647</v>
+        <v>0.5801605272283944</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.927229536782</v>
+        <v>4.010652300135757</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.247814700020705</v>
+        <v>-5.108776761097777</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.566575723550656</v>
+        <v>1.622190899119827</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3105418537746222</v>
+        <v>0.4495797926975519</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.852383140137459</v>
+        <v>3.935805903491216</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.083318365829744</v>
+        <v>-4.944280426906815</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.616801076303123</v>
+        <v>1.672416251872294</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4750381879655841</v>
+        <v>0.6140761268885138</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.935507759728118</v>
+        <v>4.018930523081876</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.110688298514176</v>
+        <v>-4.971650359591247</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.60504081366578</v>
+        <v>1.660655989234951</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4750381879655841</v>
+        <v>0.6140761268885138</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.934695470164548</v>
+        <v>4.018118233518306</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.121073493404065</v>
+        <v>-4.982035554481136</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.610755514834897</v>
+        <v>1.666370690404068</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4646529930756947</v>
+        <v>0.6036909319986244</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.938333132355686</v>
+        <v>4.021755895709445</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.13966165212629</v>
+        <v>-5.000623713203361</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.674157257122431</v>
+        <v>1.729772432691603</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4460648343534694</v>
+        <v>0.5851027732763991</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.998017242898777</v>
+        <v>4.081440006252535</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.139960198822326</v>
+        <v>-5.000922259899397</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.670906849262316</v>
+        <v>1.726522024831487</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4457662876574335</v>
+        <v>0.5848042265803632</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.994707125699454</v>
+        <v>4.078129889053212</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.039137065131898</v>
+        <v>-4.900099126208969</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.715766997677878</v>
+        <v>1.77138217324705</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4582305031417873</v>
+        <v>0.5972684420647171</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.006716549929457</v>
+        <v>4.090139313283215</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.848355704379491</v>
+        <v>-4.709317765456563</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.792208795457384</v>
+        <v>1.847823971026556</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6490118638941946</v>
+        <v>0.7880498028171244</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.121314619859445</v>
+        <v>4.204737383213203</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.829838850337671</v>
+        <v>-4.690800911414742</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.779452382811709</v>
+        <v>1.835067558380881</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6619419933194028</v>
+        <v>0.8009799322423327</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.108909543252167</v>
+        <v>4.192332306605924</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.774508262435909</v>
+        <v>-4.63547032351298</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.836551554584472</v>
+        <v>1.892166730153644</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.717272581221165</v>
+        <v>0.8563105201440948</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.177074832605283</v>
+        <v>4.26049759595904</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.762454135522946</v>
+        <v>-4.623416196600017</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.835059773251095</v>
+        <v>1.890674948820267</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7293267081341278</v>
+        <v>0.8683646470570576</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.177993876654498</v>
+        <v>4.261416640008256</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.803609255091167</v>
+        <v>-4.664571316168238</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.820478355607943</v>
+        <v>1.876093531177114</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6881715885659069</v>
+        <v>0.8272095274888367</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.155181435097701</v>
+        <v>4.238604198451459</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.700728665562574</v>
+        <v>-4.561690726639645</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.874481617297262</v>
+        <v>1.930096792866434</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7910521780944998</v>
+        <v>0.9300901170174296</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.22976081469274</v>
+        <v>4.313183578046497</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.932329058732075</v>
+        <v>-4.793291119809146</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.802044130203056</v>
+        <v>1.857659305772228</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7910521780944998</v>
+        <v>0.9300901170174296</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.249963484866334</v>
+        <v>4.333386248220092</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781704</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.950401567023686</v>
+        <v>-4.811363628100757</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.794815126886412</v>
+        <v>1.850430302455583</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7910521780944998</v>
+        <v>0.9300901170174296</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.249963484866334</v>
+        <v>4.333386248220092</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082833</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.125508399600131</v>
+        <v>-4.986470460677202</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.685024307449301</v>
+        <v>1.740639483018472</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7910521780944998</v>
+        <v>0.9300901170174296</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.2102153984598</v>
+        <v>4.293638161813558</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943584</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.094222379059675</v>
+        <v>-4.955184440136747</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.704561334662423</v>
+        <v>1.760176510231594</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8223381986349552</v>
+        <v>0.961376137557885</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.236009629781013</v>
+        <v>4.319432393134771</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677822</v>
+        <v>3.730590658677821</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.941196986946391</v>
+        <v>-4.802159048023462</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.864942491080641</v>
+        <v>1.920557666649812</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9753635907482393</v>
+        <v>1.114401529671169</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.426995864621889</v>
+        <v>4.510418627975646</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073881</v>
+        <v>3.74129851807388</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.969504300819661</v>
+        <v>-4.830466361896733</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.041085790439625</v>
+        <v>2.096700966008796</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9753635907482393</v>
+        <v>1.114401529671169</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.61446208953018</v>
+        <v>4.697884852883938</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903166</v>
+        <v>3.699135800903165</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.136097525933184</v>
+        <v>-4.997059587010255</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.943851451748298</v>
+        <v>1.99946662731747</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8087703656347169</v>
+        <v>0.9478083045576466</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.483909105816149</v>
+        <v>4.567331869169907</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568381</v>
+        <v>3.70820270456838</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.963033146550884</v>
+        <v>-4.823995207627955</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.016753606162936</v>
+        <v>2.072368781732107</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8087703656347169</v>
+        <v>0.9478083045576466</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.487585508477867</v>
+        <v>4.571008271831625</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682202</v>
+        <v>3.740601586682201</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.933787166095187</v>
+        <v>-4.794749227172258</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.02607005346871</v>
+        <v>2.081685229037881</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8087703656347169</v>
+        <v>0.9478083045576466</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.485203563601362</v>
+        <v>4.56862632695512</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539105</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.040712713973038</v>
+        <v>-4.901674775050109</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.980593073475204</v>
+        <v>2.036208249044376</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7018448177568656</v>
+        <v>0.8408827566797953</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.418341474032286</v>
+        <v>4.501764237386045</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.185731272480287</v>
+        <v>-5.046693333557358</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.924014452215539</v>
+        <v>1.979629627784711</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.556826259249617</v>
+        <v>0.6958641981725467</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.332759141071172</v>
+        <v>4.41618190442493</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969747</v>
+        <v>3.711872614969746</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.304073038265004</v>
+        <v>-5.165035099342075</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.976608985159405</v>
+        <v>2.032224160728576</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5675122978125071</v>
+        <v>0.7065502367354368</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.439102003466658</v>
+        <v>4.522524766820417</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073537</v>
+        <v>3.714899237073536</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.355483460585712</v>
+        <v>-5.216445521662783</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.95383051335706</v>
+        <v>2.009445688926232</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5675122978125071</v>
+        <v>0.7065502367354368</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.436887700592597</v>
+        <v>4.520310463946355</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720065</v>
+        <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.434902911793464</v>
+        <v>-5.295864972870535</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.921965860948249</v>
+        <v>1.977581036517421</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5675122978125071</v>
+        <v>0.7065502367354368</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.436790828666886</v>
+        <v>4.520213592020645</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581132</v>
+        <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.530365909710682</v>
+        <v>-5.282613207537583</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.883774555339406</v>
+        <v>1.982875636208645</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5675122978125071</v>
+        <v>0.7065502367354368</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.43678472222493</v>
+        <v>4.520207485578688</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500734</v>
+        <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.570385907754465</v>
+        <v>-5.322633205581367</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.865862952684503</v>
+        <v>1.964964033553743</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5274922997687232</v>
+        <v>0.666530238691653</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.410869119961271</v>
+        <v>4.494291883315029</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636269</v>
+        <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.625755069886659</v>
+        <v>-5.37800236771356</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.849449105579352</v>
+        <v>1.948550186448592</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5274922997687232</v>
+        <v>0.666530238691653</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.416602937708998</v>
+        <v>4.500025701062755</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396013</v>
+        <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.671192849717486</v>
+        <v>-5.423440147544388</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.830812356989954</v>
+        <v>1.929913437859194</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4846473090905636</v>
+        <v>0.6236852480134933</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.390434306645035</v>
+        <v>4.473857069998792</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396421</v>
+        <v>3.79029268539642</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.587967392869822</v>
+        <v>-5.340214690696723</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.883976932579339</v>
+        <v>1.983078013448579</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4846473090905636</v>
+        <v>0.6236852480134933</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.410308699495354</v>
+        <v>4.493731462849111</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299176</v>
+        <v>3.794507029299173</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.411677168264514</v>
+        <v>-5.163924466091416</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.93819372294619</v>
+        <v>2.037294803815429</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4846473090905636</v>
+        <v>0.6236852480134933</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.394009400020082</v>
+        <v>4.477432163373839</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590407</v>
+        <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.228465505131419</v>
+        <v>-4.980712802958321</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.013909337663474</v>
+        <v>2.113010418532713</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4846473090905636</v>
+        <v>0.6236852480134933</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.396440349484127</v>
+        <v>4.479863112837885</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146286</v>
+        <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.156744058117568</v>
+        <v>-4.90899135594447</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.008389102316903</v>
+        <v>2.107490183186143</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5563687561044142</v>
+        <v>0.695406695027344</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.405264403540326</v>
+        <v>4.488687166894084</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676849</v>
+        <v>3.723809890676845</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.286122840757346</v>
+        <v>-5.038370138584248</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.903553335182164</v>
+        <v>2.002654416051403</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5142669833972109</v>
+        <v>0.6533049223201406</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.326919085837176</v>
+        <v>4.410341849190934</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739466</v>
+        <v>3.715627631739462</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.319139136668091</v>
+        <v>-5.071386434494992</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.075545021703221</v>
+        <v>2.174646102572461</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.4448296067304593</v>
+        <v>0.5838675456533891</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.47045486472248</v>
+        <v>4.553877628076239</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71378272216641</v>
+        <v>3.869812766242348</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.307611501018482</v>
+        <v>-5.059858798845384</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.072077301791314</v>
+        <v>2.171178382660553</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.5038302649318218</v>
+        <v>0.6428682038547515</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.497776485471547</v>
+        <v>4.581199248825305</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.703539972471331</v>
+        <v>3.827565639493205</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.278021184104387</v>
+        <v>4.283313923622151</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.298197278927402</v>
+        <v>-5.157407540050964</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.158385848219678</v>
+        <v>2.219994483288018</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.5070942028287871</v>
+        <v>0.5978055965847817</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.582277705801659</v>
+        <v>4.64199728157302</v>
       </c>
     </row>
   </sheetData>
